--- a/Results/Phase 2/Hydrogen/hydrogen human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen human toxicity carcinogenic results.xlsx
@@ -886,7 +886,7 @@
         <v>1.068326319659683e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.245421357595172e-08</v>
+        <v>1.068326319659684e-09</v>
       </c>
       <c r="O5" t="n">
         <v>1.068326319659684e-09</v>
@@ -974,7 +974,7 @@
         <v>3.791505636484114e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.245421357595172e-08</v>
+        <v>1.642159726465053e-09</v>
       </c>
       <c r="O6" t="n">
         <v>1.642159370704956e-09</v>
@@ -1062,7 +1062,7 @@
         <v>6.234677695420113e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.245421357595172e-08</v>
+        <v>6.234677695420113e-09</v>
       </c>
       <c r="O7" t="n">
         <v>6.234480379027796e-09</v>
@@ -1150,7 +1150,7 @@
         <v>9.753405005797207e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.245421357595172e-08</v>
+        <v>6.930139086082381e-09</v>
       </c>
       <c r="O8" t="n">
         <v>7.705997075101548e-09</v>
@@ -1238,7 +1238,7 @@
         <v>6.205909495911971e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.245421357595172e-08</v>
+        <v>6.205909495911971e-09</v>
       </c>
       <c r="O9" t="n">
         <v>6.624243669308504e-09</v>
@@ -1843,7 +1843,7 @@
         <v>5.367578075049058e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.408113411448841e-09</v>
+        <v>6.40811341144884e-09</v>
       </c>
       <c r="R4" t="n">
         <v>8.405674612475223e-09</v>
@@ -1922,7 +1922,7 @@
         <v>8.891508778948836e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>6.081681528879427e-09</v>
+        <v>8.891508778948827e-10</v>
       </c>
       <c r="O5" t="n">
         <v>8.891508778948827e-10</v>
@@ -2010,7 +2010,7 @@
         <v>1.424510697621122e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.081681528879427e-09</v>
+        <v>1.425167034824697e-09</v>
       </c>
       <c r="O6" t="n">
         <v>3.211900182511789e-09</v>
@@ -2098,7 +2098,7 @@
         <v>5.136108337498835e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>6.081681528879427e-09</v>
+        <v>5.136108337498835e-09</v>
       </c>
       <c r="O7" t="n">
         <v>5.135939408861163e-09</v>
@@ -2186,7 +2186,7 @@
         <v>7.602647890677199e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>6.081681528879427e-09</v>
+        <v>5.421957239258333e-09</v>
       </c>
       <c r="O8" t="n">
         <v>6.021229965067979e-09</v>
@@ -2274,7 +2274,7 @@
         <v>4.445294207888238e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>6.081681528879427e-09</v>
+        <v>4.445294207888238e-09</v>
       </c>
       <c r="O9" t="n">
         <v>4.738458043876372e-09</v>
@@ -2870,7 +2870,7 @@
         <v>2.001245009811916e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.09313353226212e-09</v>
+        <v>8.093133532262121e-09</v>
       </c>
       <c r="O4" t="n">
         <v>7.942769246701955e-09</v>
@@ -2958,7 +2958,7 @@
         <v>9.938263953091871e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>8.093133532262121e-09</v>
+        <v>9.938263953091865e-10</v>
       </c>
       <c r="O5" t="n">
         <v>9.938263953091865e-10</v>
@@ -3046,7 +3046,7 @@
         <v>3.534748927664516e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>8.09313353226212e-09</v>
+        <v>1.53999597329318e-09</v>
       </c>
       <c r="O6" t="n">
         <v>1.539840919772376e-09</v>
@@ -3134,7 +3134,7 @@
         <v>5.756410569125858e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>8.09313353226212e-09</v>
+        <v>5.756410569125858e-09</v>
       </c>
       <c r="O7" t="n">
         <v>5.756226860515263e-09</v>
@@ -3222,7 +3222,7 @@
         <v>8.893445095278384e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>8.09313353226212e-09</v>
+        <v>6.326850600576631e-09</v>
       </c>
       <c r="O8" t="n">
         <v>7.032173053328821e-09</v>
@@ -3310,7 +3310,7 @@
         <v>5.449393411200053e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>8.09313353226212e-09</v>
+        <v>5.449393411200053e-09</v>
       </c>
       <c r="O9" t="n">
         <v>5.81396758278857e-09</v>
@@ -3697,7 +3697,7 @@
         <v>1.586703096053683e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.568891698683407e-09</v>
+        <v>1.568891698683406e-09</v>
       </c>
       <c r="D2" t="n">
         <v>1.589560035716751e-09</v>
@@ -3709,28 +3709,28 @@
         <v>1.573715492416502e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.595751186784029e-09</v>
+        <v>1.595751186784027e-09</v>
       </c>
       <c r="H2" t="n">
         <v>1.569241145298914e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.581032947537234e-09</v>
+        <v>1.581032947537233e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.585905201516893e-09</v>
+        <v>1.585905201516894e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.579164404339309e-09</v>
+        <v>1.579164404339308e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.603717692526163e-09</v>
+        <v>1.603717692526165e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.612006682625066e-09</v>
+        <v>1.612006682625062e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.570165424230639e-09</v>
+        <v>1.57016542423064e-09</v>
       </c>
       <c r="O2" t="n">
         <v>1.574579238250534e-09</v>
@@ -3739,40 +3739,40 @@
         <v>1.587965960924795e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.575918212897157e-09</v>
+        <v>1.575918212897158e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.569406324423422e-09</v>
+        <v>1.569406324423421e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.588376434985753e-09</v>
+        <v>1.588376434985755e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.571585798427124e-09</v>
+        <v>1.571585798427123e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.60111501498267e-09</v>
+        <v>1.601115014982672e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47840359517817e-09</v>
+        <v>1.478403595178176e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.594033386404337e-09</v>
+        <v>1.594033386404339e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.593811703659953e-09</v>
+        <v>1.593811703659954e-09</v>
       </c>
       <c r="Y2" t="n">
         <v>1.599702737348915e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.582643253816932e-09</v>
+        <v>1.582643253816931e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.573952124695142e-09</v>
+        <v>1.573952124695141e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.63790885405597e-09</v>
+        <v>1.637908854055969e-09</v>
       </c>
     </row>
     <row r="3">
@@ -3791,7 +3791,7 @@
         <v>1.57401429973882e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>2.05608402429842e-09</v>
+        <v>2.056084024298422e-09</v>
       </c>
       <c r="F3" t="n">
         <v>1.57401429973882e-09</v>
@@ -3806,7 +3806,7 @@
         <v>1.57401429973882e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.570316130517201e-09</v>
+        <v>1.570316130517203e-09</v>
       </c>
       <c r="K3" t="n">
         <v>1.57401429973882e-09</v>
@@ -3842,7 +3842,7 @@
         <v>1.57401429973882e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.473348151013622e-09</v>
+        <v>1.473348151013623e-09</v>
       </c>
       <c r="W3" t="n">
         <v>1.57401429973882e-09</v>
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.584353061318022e-09</v>
+        <v>9.584353061317992e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>5.714953282594605e-09</v>
+        <v>5.71495328259459e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.115800408654521e-08</v>
+        <v>1.115800408654529e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.166287345724128e-09</v>
+        <v>5.166287345724129e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.066044565365325e-09</v>
+        <v>7.066044565365329e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.17049211298631e-08</v>
+        <v>1.170492112986308e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.036407416634451e-09</v>
+        <v>6.036407416634458e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>9.020281559342322e-09</v>
+        <v>9.020281559342274e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.055543199862852e-08</v>
+        <v>1.055543199862856e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.10283598163445e-09</v>
+        <v>8.102835981634377e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4230368557608e-08</v>
+        <v>1.42303685576082e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.732515063739532e-08</v>
+        <v>1.73251506373953e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.959213087288713e-09</v>
+        <v>5.959213087288716e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>6.64498633813836e-09</v>
+        <v>6.644986338138467e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>9.818127737271049e-09</v>
+        <v>9.818127737271053e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.407227155074747e-09</v>
+        <v>7.407227155074715e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>5.972588609244592e-09</v>
+        <v>5.972588609244593e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.003034977279702e-08</v>
+        <v>1.003034977279704e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.462731166875287e-09</v>
+        <v>6.462731166875294e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33169980249029e-08</v>
+        <v>1.331699802490413e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>7.042720126420285e-09</v>
+        <v>7.042720126420459e-09</v>
       </c>
       <c r="W4" t="n">
         <v>1.192855288782878e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.21431147132649e-08</v>
+        <v>1.214311471326486e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.332264371415094e-08</v>
+        <v>1.332264371415088e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.420764170295182e-09</v>
+        <v>8.420764170295119e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.853620295327893e-09</v>
+        <v>6.853620295327875e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.526838342418685e-08</v>
+        <v>2.526838342418674e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.433954856812245e-10</v>
+        <v>9.433954856812262e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>9.433954856812247e-10</v>
+        <v>9.433954856812255e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="J5" t="n">
         <v>9.430835879588066e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>9.433954856812257e-10</v>
+        <v>9.433954856812245e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>5.959213087288713e-09</v>
+        <v>9.433954856812255e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>9.433954856812247e-10</v>
+        <v>9.433954856812255e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>9.433954856812247e-10</v>
+        <v>9.433954856812255e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.433954856812247e-10</v>
+        <v>9.433954856812255e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>9.379373792650085e-10</v>
+        <v>9.379373792650083e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>9.426110199461498e-10</v>
+        <v>9.426110199461484e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>9.433954856812247e-10</v>
+        <v>9.433954856812255e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>9.433954856812245e-10</v>
+        <v>9.433954856812262e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.379373792650085e-10</v>
+        <v>9.379373792650083e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.433954856812251e-10</v>
+        <v>9.433954856812241e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.433954856812247e-10</v>
+        <v>9.433954856812255e-10</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.310062222278081e-09</v>
+        <v>3.310062222278098e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.458420896599041e-09</v>
+        <v>1.45842089659904e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>3.310062222278082e-09</v>
+        <v>3.3100622222781e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>3.310062222278082e-09</v>
+        <v>3.3100622222781e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.458420896599041e-09</v>
+        <v>1.45842089659904e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.458420896599041e-09</v>
+        <v>1.45842089659904e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.458420896599041e-09</v>
+        <v>1.45842089659904e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.458420896599041e-09</v>
+        <v>1.45842089659904e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.309750324555659e-09</v>
+        <v>3.309750324555686e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>3.310062222278082e-09</v>
+        <v>3.3100622222781e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.310062222278081e-09</v>
+        <v>3.310062222278098e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.458420896599041e-09</v>
+        <v>1.45842089659904e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>5.959213087288713e-09</v>
+        <v>1.45924102313092e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>3.297612559832871e-09</v>
+        <v>3.297612559832857e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>3.297678725049108e-09</v>
+        <v>3.297678725049104e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.310062222278082e-09</v>
+        <v>3.3100622222781e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.458420896599041e-09</v>
+        <v>1.45842089659904e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.310062222278082e-09</v>
+        <v>3.3100622222781e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.458420896599041e-09</v>
+        <v>1.45842089659904e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.458420896599041e-09</v>
+        <v>1.45842089659904e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>3.309277756543012e-09</v>
+        <v>3.30927775654302e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>3.297585229829787e-09</v>
+        <v>3.297585229829779e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.458420896599041e-09</v>
+        <v>1.45842089659904e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.50461232064235e-09</v>
+        <v>1.504612320642348e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.310062222278082e-09</v>
+        <v>3.3100622222781e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.310062222278082e-09</v>
+        <v>3.3100622222781e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.46351977568365e-09</v>
+        <v>1.463519775683657e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.33813447103183e-09</v>
+        <v>5.33813447103184e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.337822573309411e-09</v>
+        <v>5.337822573309405e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.33813447103183e-09</v>
+        <v>5.33813447103184e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>5.959213087288713e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>5.337963596742716e-09</v>
+        <v>5.337963596742719e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>5.337963596742716e-09</v>
+        <v>5.337963596742719e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>5.338166962386747e-09</v>
+        <v>5.338166962386744e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>5.337350005296758e-09</v>
+        <v>5.337350005296756e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>5.33813447103183e-09</v>
+        <v>5.33813447103184e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.338134471031827e-09</v>
+        <v>5.338134471031838e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.122875390115649e-09</v>
+        <v>5.12287539011566e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.140865623134437e-09</v>
+        <v>8.140865623134455e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>8.140865623134437e-09</v>
+        <v>8.140865623134455e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>6.533874849116798e-09</v>
+        <v>6.533874849116815e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>5.59304299647103e-09</v>
+        <v>5.593042996471035e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.766665558357484e-09</v>
+        <v>8.766665558357476e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.140865623134437e-09</v>
+        <v>8.140865623134455e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.140865623134437e-09</v>
+        <v>8.140865623134455e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.140553725412027e-09</v>
+        <v>8.140553725412021e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>8.140865623134437e-09</v>
+        <v>8.140865623134455e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>8.14086562313444e-09</v>
+        <v>8.140865623134458e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>8.140865623134257e-09</v>
+        <v>8.140865623134271e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>5.959213087288713e-09</v>
+        <v>5.801418293880623e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>6.444318733248294e-09</v>
+        <v>6.444318733248302e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>6.286728300884511e-09</v>
+        <v>6.286728300884519e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.529771426960441e-09</v>
+        <v>4.529771426960453e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>8.140865623134437e-09</v>
+        <v>8.140865623134455e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>8.140865623134437e-09</v>
+        <v>8.140865623134455e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>8.140865623134437e-09</v>
+        <v>8.140865623134455e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>6.667982474680743e-09</v>
+        <v>6.667982474680756e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>7.315392753081572e-09</v>
+        <v>7.315392753081587e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>8.141458745086597e-09</v>
+        <v>8.141458745086606e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>4.806376228896104e-09</v>
+        <v>4.806376228896125e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.114185423156286e-08</v>
+        <v>1.114185423156287e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.066814672067662e-09</v>
+        <v>5.066814672067682e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.140865623134437e-09</v>
+        <v>8.140865623134455e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.129340878212505e-08</v>
+        <v>1.129340878212508e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.899803506149309e-09</v>
+        <v>3.899803506149297e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.650042278586883e-09</v>
+        <v>4.65004227858687e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>2.626713068320883e-09</v>
+        <v>2.626713068320868e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.875147752224168e-09</v>
+        <v>4.875147752224144e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>4.874834711749946e-09</v>
+        <v>4.874834711749953e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>4.875146609472357e-09</v>
+        <v>4.875146609472348e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>5.959213087288713e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>5.198375558269537e-09</v>
+        <v>5.198375558269516e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>5.268672060428977e-09</v>
+        <v>5.268672060428965e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.875147752224168e-09</v>
+        <v>4.875147752224144e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>5.999887419592711e-09</v>
+        <v>5.999887419592709e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>4.875146609472357e-09</v>
+        <v>4.875146609472348e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.287101902835511e-09</v>
+        <v>4.287101902835492e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.875146609472363e-09</v>
+        <v>4.875146609472344e-09</v>
       </c>
     </row>
     <row r="10">
@@ -4401,16 +4401,16 @@
         <v>1.412331151567311e-09</v>
       </c>
       <c r="C10" t="n">
-        <v>1.519160668596616e-09</v>
+        <v>1.519160668596617e-09</v>
       </c>
       <c r="D10" t="n">
-        <v>1.398164114030605e-09</v>
+        <v>1.398164114030601e-09</v>
       </c>
       <c r="E10" t="n">
-        <v>1.960799857343349e-09</v>
+        <v>1.960799857343351e-09</v>
       </c>
       <c r="F10" t="n">
-        <v>1.491404230856947e-09</v>
+        <v>1.491404230856949e-09</v>
       </c>
       <c r="G10" t="n">
         <v>1.358625428868232e-09</v>
@@ -4422,13 +4422,13 @@
         <v>1.448356828959259e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>1.392375568731999e-09</v>
+        <v>1.392375568732e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>1.458887117388976e-09</v>
+        <v>1.458887117388977e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>1.312789529123879e-09</v>
+        <v>1.312789529123883e-09</v>
       </c>
       <c r="M10" t="n">
         <v>1.267867395152747e-09</v>
@@ -4437,46 +4437,46 @@
         <v>1.511484438178626e-09</v>
       </c>
       <c r="O10" t="n">
-        <v>1.484354851066836e-09</v>
+        <v>1.484354851066835e-09</v>
       </c>
       <c r="P10" t="n">
-        <v>1.404473597421433e-09</v>
+        <v>1.404473597421431e-09</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.477813181600021e-09</v>
+        <v>1.47781318160002e-09</v>
       </c>
       <c r="R10" t="n">
-        <v>1.516462726717418e-09</v>
+        <v>1.516462726717417e-09</v>
       </c>
       <c r="S10" t="n">
-        <v>1.402921511148906e-09</v>
+        <v>1.402921511148903e-09</v>
       </c>
       <c r="T10" t="n">
-        <v>1.503496893988743e-09</v>
+        <v>1.503496893988742e-09</v>
       </c>
       <c r="U10" t="n">
-        <v>1.327925841709768e-09</v>
+        <v>1.327925841709757e-09</v>
       </c>
       <c r="V10" t="n">
-        <v>1.365002594396748e-09</v>
+        <v>1.365002594396753e-09</v>
       </c>
       <c r="W10" t="n">
-        <v>1.370389976674066e-09</v>
+        <v>1.370389976674068e-09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.373061338719292e-09</v>
+        <v>1.373061338719294e-09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.337320537554608e-09</v>
+        <v>1.337320537554607e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.436642008589456e-09</v>
+        <v>1.436642008589457e-09</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.488983071791855e-09</v>
+        <v>1.488983071791856e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.115062799416362e-09</v>
+        <v>1.115062799416365e-09</v>
       </c>
     </row>
     <row r="11">
@@ -4486,28 +4486,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.513136748382023e-09</v>
+        <v>1.513136748382026e-09</v>
       </c>
       <c r="C11" t="n">
-        <v>1.543933121705552e-09</v>
+        <v>1.543933121705555e-09</v>
       </c>
       <c r="D11" t="n">
-        <v>1.509547640818222e-09</v>
+        <v>1.509547640818224e-09</v>
       </c>
       <c r="E11" t="n">
-        <v>2.004805139527693e-09</v>
+        <v>2.004805139527692e-09</v>
       </c>
       <c r="F11" t="n">
-        <v>1.536127647812579e-09</v>
+        <v>1.536127647812581e-09</v>
       </c>
       <c r="G11" t="n">
-        <v>1.497748564134303e-09</v>
+        <v>1.497748564134304e-09</v>
       </c>
       <c r="H11" t="n">
         <v>1.543573125431041e-09</v>
       </c>
       <c r="I11" t="n">
-        <v>1.523858397885933e-09</v>
+        <v>1.523858397885935e-09</v>
       </c>
       <c r="J11" t="n">
         <v>1.504941678841703e-09</v>
@@ -4516,55 +4516,55 @@
         <v>1.526781169481569e-09</v>
       </c>
       <c r="L11" t="n">
-        <v>1.484859589422417e-09</v>
+        <v>1.484859589422418e-09</v>
       </c>
       <c r="M11" t="n">
-        <v>1.472708865406104e-09</v>
+        <v>1.472708865406103e-09</v>
       </c>
       <c r="N11" t="n">
         <v>1.541714137949908e-09</v>
       </c>
       <c r="O11" t="n">
-        <v>1.53378390337707e-09</v>
+        <v>1.533783903377072e-09</v>
       </c>
       <c r="P11" t="n">
-        <v>1.510824401076225e-09</v>
+        <v>1.510824401076222e-09</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.532146397569231e-09</v>
+        <v>1.53214639756923e-09</v>
       </c>
       <c r="R11" t="n">
-        <v>1.543220175292703e-09</v>
+        <v>1.543220175292702e-09</v>
       </c>
       <c r="S11" t="n">
-        <v>1.510528670936977e-09</v>
+        <v>1.510528670936978e-09</v>
       </c>
       <c r="T11" t="n">
-        <v>1.539500154085199e-09</v>
+        <v>1.539500154085197e-09</v>
       </c>
       <c r="U11" t="n">
-        <v>1.489143982342068e-09</v>
+        <v>1.489143982342071e-09</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42910602164069e-09</v>
+        <v>1.4291060216407e-09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.501383670497659e-09</v>
+        <v>1.50138367049766e-09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.502377465996978e-09</v>
+        <v>1.50237746599698e-09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.492006321256834e-09</v>
+        <v>1.492006321256835e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.520138423564452e-09</v>
+        <v>1.520138423564453e-09</v>
       </c>
       <c r="AA11" t="n">
         <v>1.535262645000828e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.429084458817604e-09</v>
+        <v>1.429084458817602e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.566083222700435e-09</v>
+        <v>1.566083222700432e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.549941307929062e-09</v>
+        <v>1.549941307929059e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.567134094019674e-09</v>
+        <v>1.567134094019676e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.034707716299627e-09</v>
+        <v>2.034707716299626e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.557804379990995e-09</v>
+        <v>1.557804379990991e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.575069045925843e-09</v>
+        <v>1.575069045925844e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.55221975546552e-09</v>
+        <v>1.552219755465518e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.56119848200702e-09</v>
+        <v>1.561198482007022e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.567074115857985e-09</v>
+        <v>1.567074115857986e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.560794379603678e-09</v>
+        <v>1.560794379603681e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.580507892291115e-09</v>
+        <v>1.580507892291113e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.588397667798798e-09</v>
+        <v>1.588397667798796e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.549512365952901e-09</v>
+        <v>1.549512365952898e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.555314822150387e-09</v>
+        <v>1.555314822150383e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.568111570828018e-09</v>
+        <v>1.568111570828019e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.557289087877064e-09</v>
+        <v>1.557289087877065e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.555570265473115e-09</v>
+        <v>1.555570265473113e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.569829304167312e-09</v>
+        <v>1.569829304167311e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.556031573776306e-09</v>
+        <v>1.556031573776305e-09</v>
       </c>
       <c r="U2" t="n">
         <v>1.585097869264083e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.466014906585785e-09</v>
+        <v>1.466014906585784e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.576294292757732e-09</v>
+        <v>1.576294292757728e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.579760370731436e-09</v>
+        <v>1.579760370731435e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.600191058503783e-09</v>
+        <v>1.600191058503786e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.564557189880078e-09</v>
+        <v>1.564557189880077e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.557077813621379e-09</v>
+        <v>1.55707781362138e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.615330851299476e-09</v>
+        <v>1.615330851299485e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>2.044962465245288e-09</v>
+        <v>2.044962465245291e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.552599006170873e-09</v>
+        <v>1.552599006170876e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.454466781765547e-09</v>
+        <v>1.454466781765545e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.555938659571472e-09</v>
+        <v>1.555938659571473e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.767316064401293e-09</v>
+        <v>8.767316064401331e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>5.417381484833757e-09</v>
+        <v>5.417381484833748e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.74423986410414e-09</v>
+        <v>9.744239864104272e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.476970247811919e-09</v>
+        <v>4.476970247811922e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.515762976718254e-09</v>
+        <v>7.515762976718283e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.081733066557345e-08</v>
+        <v>1.081733066557323e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.238483995792972e-09</v>
+        <v>6.238483995792977e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.411658258142422e-09</v>
+        <v>8.411658258142396e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.008231488795147e-08</v>
+        <v>1.008231488795127e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.952261657749179e-09</v>
+        <v>7.952261657749143e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.255792844843538e-08</v>
+        <v>1.255792844843537e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.531423334339807e-08</v>
+        <v>1.531423334339765e-08</v>
       </c>
       <c r="N4" t="n">
         <v>5.21162451352233e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>6.301659937743024e-09</v>
+        <v>6.301659937743042e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>9.167635270237187e-09</v>
+        <v>9.167635270237009e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.113514981216398e-09</v>
+        <v>7.113514981216394e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.035281788734032e-09</v>
+        <v>7.035281788734019e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>9.764775308514302e-09</v>
+        <v>9.764775308514378e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.046960367981269e-09</v>
+        <v>7.046960367981285e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.342280697169022e-08</v>
+        <v>1.342280697169018e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.377626432646033e-09</v>
+        <v>8.377626432645979e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.194320298385542e-08</v>
+        <v>1.194320298385538e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.282948876301746e-08</v>
+        <v>1.282948876301733e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.816559924662982e-08</v>
+        <v>1.816559924662993e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.129270701740919e-09</v>
+        <v>8.129270701740911e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.084291141925338e-09</v>
+        <v>7.084291141925296e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.362736246872739e-08</v>
+        <v>2.36273624687271e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.419009904573067e-10</v>
+        <v>9.419009904573121e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>9.419009904573059e-10</v>
+        <v>9.41900990457309e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>9.416550529119368e-10</v>
+        <v>9.416550529119391e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>9.419009904573054e-10</v>
+        <v>9.419009904573133e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>5.21162451352233e-09</v>
+        <v>9.41900990457309e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>9.419009904573059e-10</v>
+        <v>9.41900990457309e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>9.419009904573059e-10</v>
+        <v>9.41900990457309e-10</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.419009904573059e-10</v>
+        <v>9.41900990457309e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>9.395673304278652e-10</v>
+        <v>9.39567330427867e-10</v>
       </c>
       <c r="V5" t="n">
-        <v>9.415356554275651e-10</v>
+        <v>9.415356554275612e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>9.419009904573059e-10</v>
+        <v>9.41900990457309e-10</v>
       </c>
       <c r="X5" t="n">
-        <v>9.419009904573069e-10</v>
+        <v>9.419009904573098e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.395673304278652e-10</v>
+        <v>9.39567330427867e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.419009904573048e-10</v>
+        <v>9.419009904573131e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.419009904573059e-10</v>
+        <v>9.41900990457309e-10</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.464265365419074e-09</v>
+        <v>1.464265365419068e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.464265365419074e-09</v>
+        <v>1.464265365419068e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>3.30954754461709e-09</v>
+        <v>3.309547544617102e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>3.30954754461709e-09</v>
+        <v>3.309547544617102e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.464265365419074e-09</v>
+        <v>1.464265365419068e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.464265365419074e-09</v>
+        <v>1.464265365419068e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>3.30954754461709e-09</v>
+        <v>3.309547544617102e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.464265365419074e-09</v>
+        <v>1.464265365419068e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.30930160707172e-09</v>
+        <v>3.309301607071704e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>3.30954754461709e-09</v>
+        <v>3.309547544617102e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.464265365419074e-09</v>
+        <v>1.464265365419068e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.464265365419074e-09</v>
+        <v>1.464265365419068e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>5.21162451352233e-09</v>
+        <v>1.465564630483115e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.465452111407867e-09</v>
+        <v>1.46545211140788e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>3.297569954077379e-09</v>
+        <v>3.297569954077382e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.30954754461709e-09</v>
+        <v>3.309547544617102e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>3.30954754461709e-09</v>
+        <v>3.309547544617102e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.464265365419074e-09</v>
+        <v>1.464265365419068e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>3.30954754461709e-09</v>
+        <v>3.309547544617102e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>3.30954754461709e-09</v>
+        <v>3.309547544617102e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.463900030389339e-09</v>
+        <v>1.463900030389324e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.519315854904077e-09</v>
+        <v>1.519315854904081e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.464265365419074e-09</v>
+        <v>1.464265365419068e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.511345207080475e-09</v>
+        <v>1.51134520708047e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.464265365419074e-09</v>
+        <v>1.464265365419068e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.30954754461709e-09</v>
+        <v>3.309547544617102e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.469146814746251e-09</v>
+        <v>1.469146814746252e-09</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.310000492907887e-09</v>
+        <v>5.310000492907877e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>5.309754555362522e-09</v>
+        <v>5.309754555362521e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>5.310000492907888e-09</v>
+        <v>5.310000492907877e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>5.21162451352233e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>5.309829752719225e-09</v>
+        <v>5.309829752719203e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>5.309829752719225e-09</v>
+        <v>5.309829752719203e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>5.310586487664764e-09</v>
+        <v>5.31058648766475e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>5.309635157878155e-09</v>
+        <v>5.309635157878132e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>5.310000492907888e-09</v>
+        <v>5.310000492907877e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.310000492907885e-09</v>
+        <v>5.310000492907869e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.06093459368061e-09</v>
+        <v>5.060934593680597e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>8.036282372285708e-09</v>
+        <v>8.036282372285688e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>8.036282372285708e-09</v>
+        <v>8.036282372285688e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>6.451997447373755e-09</v>
+        <v>6.451997447373757e-09</v>
       </c>
       <c r="F8" t="n">
         <v>5.524459004009023e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>8.653240116794675e-09</v>
+        <v>8.65324011679467e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>8.036282372285708e-09</v>
+        <v>8.036282372285688e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>8.036282372285708e-09</v>
+        <v>8.036282372285688e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>8.03603643474033e-09</v>
+        <v>8.036036434740322e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>8.036282372285708e-09</v>
+        <v>8.036282372285688e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>8.036282372285711e-09</v>
+        <v>8.036282372285691e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>8.036282372285586e-09</v>
+        <v>8.036282372285574e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>5.21162451352233e-09</v>
+        <v>5.729890079124562e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>6.363706707551369e-09</v>
+        <v>6.363706707551353e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>6.208342936745965e-09</v>
+        <v>6.208342936745942e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.476210846089865e-09</v>
+        <v>4.476210846089871e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>8.036282372285708e-09</v>
+        <v>8.036282372285688e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>8.036282372285708e-09</v>
+        <v>8.036282372285688e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>8.036282372285708e-09</v>
+        <v>8.036282372285688e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>6.584641284301305e-09</v>
+        <v>6.584641284301304e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>7.223356465067006e-09</v>
+        <v>7.223356465066987e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>8.036867113753565e-09</v>
+        <v>8.036867113753562e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>4.748907382334213e-09</v>
+        <v>4.748907382334207e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.099560619240389e-08</v>
+        <v>1.099560619240387e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.005665981117974e-09</v>
+        <v>5.005665981117978e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.036282372285708e-09</v>
+        <v>8.036282372285688e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.114428192191802e-08</v>
+        <v>1.114428192191801e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.772250655824548e-09</v>
+        <v>3.772250655824553e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.494255310581942e-09</v>
+        <v>4.494255310581945e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>2.547071078591037e-09</v>
+        <v>2.547071078591041e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.7108892753255e-09</v>
+        <v>4.71088927532549e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>4.710642198649444e-09</v>
+        <v>4.710642198649437e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.71088813619484e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>5.21162451352233e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>5.021952884786182e-09</v>
+        <v>5.021952884786201e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>5.08960388289091e-09</v>
+        <v>5.08960388289092e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.7108892753255e-09</v>
+        <v>4.71088927532549e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>5.793690621897539e-09</v>
+        <v>5.793690621897495e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.71088813619484e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.144973654769233e-09</v>
+        <v>4.144973654769211e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.71088813619481e-09</v>
+        <v>4.710888136194842e-09</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.411243320933057e-09</v>
+        <v>1.41124332093306e-09</v>
       </c>
       <c r="C10" t="n">
         <v>1.508040048705038e-09</v>
       </c>
       <c r="D10" t="n">
-        <v>1.407393577978972e-09</v>
+        <v>1.407393577978976e-09</v>
       </c>
       <c r="E10" t="n">
         <v>1.964668110034632e-09</v>
       </c>
       <c r="F10" t="n">
-        <v>1.462525809240126e-09</v>
+        <v>1.462525809240129e-09</v>
       </c>
       <c r="G10" t="n">
-        <v>1.357898383922038e-09</v>
+        <v>1.357898383922046e-09</v>
       </c>
       <c r="H10" t="n">
         <v>1.495202887131122e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>1.442383926607473e-09</v>
+        <v>1.442383926607474e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>1.383256609970406e-09</v>
+        <v>1.383256609970408e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4443639603545e-09</v>
+        <v>1.444363960354503e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>1.326906270729433e-09</v>
+        <v>1.326906270729435e-09</v>
       </c>
       <c r="M10" t="n">
-        <v>1.283896797018201e-09</v>
+        <v>1.283896797018207e-09</v>
       </c>
       <c r="N10" t="n">
-        <v>1.510400800445574e-09</v>
+        <v>1.510400800445576e-09</v>
       </c>
       <c r="O10" t="n">
-        <v>1.475212896853168e-09</v>
+        <v>1.475212896853169e-09</v>
       </c>
       <c r="P10" t="n">
-        <v>1.398856387248282e-09</v>
+        <v>1.398856387248284e-09</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.464815644920219e-09</v>
+        <v>1.464815644920217e-09</v>
       </c>
       <c r="R10" t="n">
-        <v>1.475467316835201e-09</v>
+        <v>1.475467316835199e-09</v>
       </c>
       <c r="S10" t="n">
-        <v>1.389488173486062e-09</v>
+        <v>1.389488173486061e-09</v>
       </c>
       <c r="T10" t="n">
-        <v>1.472483273233146e-09</v>
+        <v>1.472483273233148e-09</v>
       </c>
       <c r="U10" t="n">
-        <v>1.299510463189772e-09</v>
+        <v>1.299510463189771e-09</v>
       </c>
       <c r="V10" t="n">
-        <v>1.309602305495676e-09</v>
+        <v>1.309602305495672e-09</v>
       </c>
       <c r="W10" t="n">
-        <v>1.352165017905961e-09</v>
+        <v>1.352165017905962e-09</v>
       </c>
       <c r="X10" t="n">
-        <v>1.33321535087744e-09</v>
+        <v>1.333215350877439e-09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.211691778739576e-09</v>
+        <v>1.21169177873958e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.420477977153768e-09</v>
+        <v>1.420477977153771e-09</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.465658449271812e-09</v>
+        <v>1.46565844927181e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.125176523589041e-09</v>
+        <v>1.125176523589038e-09</v>
       </c>
     </row>
     <row r="11">
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.500246382503271e-09</v>
+        <v>1.500246382503266e-09</v>
       </c>
       <c r="C11" t="n">
         <v>1.52814728734102e-09</v>
@@ -5531,76 +5531,76 @@
         <v>1.499545608510001e-09</v>
       </c>
       <c r="E11" t="n">
-        <v>1.998173528795849e-09</v>
+        <v>1.998173528795846e-09</v>
       </c>
       <c r="F11" t="n">
-        <v>1.51530123540114e-09</v>
+        <v>1.515301235401142e-09</v>
       </c>
       <c r="G11" t="n">
-        <v>1.48496008938844e-09</v>
+        <v>1.484960089388441e-09</v>
       </c>
       <c r="H11" t="n">
-        <v>1.524584785451737e-09</v>
+        <v>1.524584785451738e-09</v>
       </c>
       <c r="I11" t="n">
-        <v>1.509530716630939e-09</v>
+        <v>1.50953071663094e-09</v>
       </c>
       <c r="J11" t="n">
-        <v>1.490022785924576e-09</v>
+        <v>1.490022785924575e-09</v>
       </c>
       <c r="K11" t="n">
         <v>1.510027535892488e-09</v>
       </c>
       <c r="L11" t="n">
-        <v>1.476297425485071e-09</v>
+        <v>1.476297425485074e-09</v>
       </c>
       <c r="M11" t="n">
-        <v>1.464617753391082e-09</v>
+        <v>1.464617753391084e-09</v>
       </c>
       <c r="N11" t="n">
         <v>1.528792494930071e-09</v>
       </c>
       <c r="O11" t="n">
-        <v>1.518584342855816e-09</v>
+        <v>1.518584342855815e-09</v>
       </c>
       <c r="P11" t="n">
-        <v>1.496638636329468e-09</v>
+        <v>1.496638636329467e-09</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.515827825818925e-09</v>
+        <v>1.515827825818926e-09</v>
       </c>
       <c r="R11" t="n">
         <v>1.518955548081157e-09</v>
       </c>
       <c r="S11" t="n">
-        <v>1.494093802552226e-09</v>
+        <v>1.494093802552228e-09</v>
       </c>
       <c r="T11" t="n">
-        <v>1.518059107035833e-09</v>
+        <v>1.518059107035831e-09</v>
       </c>
       <c r="U11" t="n">
         <v>1.468422222722236e-09</v>
       </c>
       <c r="V11" t="n">
-        <v>1.400101108227297e-09</v>
+        <v>1.400101108227299e-09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.483576636411859e-09</v>
+        <v>1.483576636411857e-09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.478420555498582e-09</v>
+        <v>1.478420555498586e-09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.443557630675552e-09</v>
+        <v>1.443557630675553e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.502922147692442e-09</v>
+        <v>1.502922147692443e-09</v>
       </c>
       <c r="AA11" t="n">
         <v>1.516000030229077e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.419332706669995e-09</v>
+        <v>1.419332706669996e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>9.123323009421825e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>8.802507646656722e-09</v>
+        <v>9.123323009421837e-10</v>
       </c>
       <c r="O5" t="n">
         <v>9.123323009421837e-10</v>
@@ -6154,7 +6154,7 @@
         <v>3.411399159105629e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>8.802507646656722e-09</v>
+        <v>1.490489901695529e-09</v>
       </c>
       <c r="O6" t="n">
         <v>3.401646867933325e-09</v>
@@ -6242,7 +6242,7 @@
         <v>5.457213614694828e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>8.802507646656722e-09</v>
+        <v>5.457213614694828e-09</v>
       </c>
       <c r="O7" t="n">
         <v>5.45703215507824e-09</v>
@@ -6330,7 +6330,7 @@
         <v>8.135077721473853e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>8.802507646656722e-09</v>
+        <v>5.792798648689301e-09</v>
       </c>
       <c r="O8" t="n">
         <v>6.436477275765342e-09</v>
@@ -6418,7 +6418,7 @@
         <v>5.014788741528944e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>8.802507646656722e-09</v>
+        <v>5.014788741528944e-09</v>
       </c>
       <c r="O9" t="n">
         <v>5.349133960228545e-09</v>
@@ -6817,7 +6817,7 @@
         <v>1.422189547720074e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.418753473936547e-09</v>
+        <v>1.418753473936546e-09</v>
       </c>
       <c r="H2" t="n">
         <v>1.421049682521048e-09</v>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.72084890705554e-09</v>
+        <v>6.720848907055541e-09</v>
       </c>
       <c r="C4" t="n">
         <v>5.884428580754158e-09</v>
@@ -6996,13 +6996,13 @@
         <v>5.959071763257369e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2735477336171e-09</v>
+        <v>7.273547733617101e-09</v>
       </c>
       <c r="I4" t="n">
         <v>7.595590660037969e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.453281004329702e-09</v>
+        <v>6.453281004329701e-09</v>
       </c>
       <c r="K4" t="n">
         <v>6.983990568544275e-09</v>
@@ -7023,7 +7023,7 @@
         <v>5.195240454345837e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.999372499974692e-09</v>
+        <v>5.999372499974693e-09</v>
       </c>
       <c r="R4" t="n">
         <v>7.676471700353124e-09</v>
@@ -7069,40 +7069,40 @@
         <v>8.604315353529652e-10</v>
       </c>
       <c r="C5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="F5" t="n">
         <v>8.604315353529636e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="J5" t="n">
         <v>8.601592800142974e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>6.35972894395063e-09</v>
+        <v>8.604315353529635e-10</v>
       </c>
       <c r="O5" t="n">
         <v>8.604315353529636e-10</v>
@@ -7114,34 +7114,34 @@
         <v>8.604315353529636e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>8.583760661308907e-10</v>
+        <v>8.583760661308908e-10</v>
       </c>
       <c r="V5" t="n">
         <v>8.598798614014453e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>8.604315353529634e-10</v>
+        <v>8.604315353529635e-10</v>
       </c>
       <c r="X5" t="n">
         <v>8.604315353529636e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.583760661308907e-10</v>
+        <v>8.583760661308908e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.604315353529647e-10</v>
+        <v>8.604315353529648e-10</v>
       </c>
       <c r="AB5" t="n">
         <v>8.604315353529636e-10</v>
@@ -7190,7 +7190,7 @@
         <v>3.184119208629533e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.35972894395063e-09</v>
+        <v>1.40598879496448e-09</v>
       </c>
       <c r="O6" t="n">
         <v>3.175415364543967e-09</v>
@@ -7278,7 +7278,7 @@
         <v>5.036899262457584e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>6.35972894395063e-09</v>
+        <v>5.036899262457584e-09</v>
       </c>
       <c r="O7" t="n">
         <v>5.036731230162146e-09</v>
@@ -7299,7 +7299,7 @@
         <v>5.036899262457584e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>5.03739750218616e-09</v>
+        <v>5.037397502186161e-09</v>
       </c>
       <c r="V7" t="n">
         <v>5.036347588506057e-09</v>
@@ -7366,7 +7366,7 @@
         <v>7.364703814537956e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>6.35972894395063e-09</v>
+        <v>5.253874056274478e-09</v>
       </c>
       <c r="O8" t="n">
         <v>5.833948402042975e-09</v>
@@ -7390,7 +7390,7 @@
         <v>6.036129217194395e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>6.620467344726407e-09</v>
+        <v>6.620467344726406e-09</v>
       </c>
       <c r="W8" t="n">
         <v>7.365238974860768e-09</v>
@@ -7408,7 +7408,7 @@
         <v>7.364703814537984e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.020917132226645e-08</v>
+        <v>1.020917132226644e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7433,7 +7433,7 @@
         <v>2.39833877784744e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>4.435957712863508e-09</v>
+        <v>4.435957712863509e-09</v>
       </c>
       <c r="H9" t="n">
         <v>4.435956539563905e-09</v>
@@ -7454,7 +7454,7 @@
         <v>4.435956539563905e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>6.35972894395063e-09</v>
+        <v>4.435956539563905e-09</v>
       </c>
       <c r="O9" t="n">
         <v>4.728879318564061e-09</v>
@@ -7463,7 +7463,7 @@
         <v>4.792584742115335e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.435957712863508e-09</v>
+        <v>4.435957712863509e-09</v>
       </c>
       <c r="R9" t="n">
         <v>4.435956539563905e-09</v>
@@ -7666,7 +7666,7 @@
         <v>1.374894323868977e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.381153101682101e-09</v>
+        <v>1.381153101682102e-09</v>
       </c>
       <c r="AA11" t="n">
         <v>1.381884196080738e-09</v>
@@ -8050,7 +8050,7 @@
         <v>6.785890087581342e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>6.352317272197162e-09</v>
+        <v>6.352317272197165e-09</v>
       </c>
       <c r="O4" t="n">
         <v>5.586140202508284e-09</v>
@@ -8138,7 +8138,7 @@
         <v>8.631895509824836e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>6.352317272197165e-09</v>
+        <v>8.631895509824849e-10</v>
       </c>
       <c r="O5" t="n">
         <v>8.631895509824849e-10</v>
@@ -8226,7 +8226,7 @@
         <v>3.20039273464556e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.352317272197162e-09</v>
+        <v>1.413478822785911e-09</v>
       </c>
       <c r="O6" t="n">
         <v>1.413343901892447e-09</v>
@@ -8314,7 +8314,7 @@
         <v>5.030138451007435e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>6.352317272197162e-09</v>
+        <v>5.030138451007435e-09</v>
       </c>
       <c r="O7" t="n">
         <v>5.029970705708343e-09</v>
@@ -8402,7 +8402,7 @@
         <v>7.319471411720602e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>6.352317272197164e-09</v>
+        <v>5.222752650329515e-09</v>
       </c>
       <c r="O8" t="n">
         <v>5.798949171623523e-09</v>
@@ -8490,7 +8490,7 @@
         <v>4.326189581981912e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>6.352317272197162e-09</v>
+        <v>4.326189581981912e-09</v>
       </c>
       <c r="O9" t="n">
         <v>4.611115266929022e-09</v>
@@ -9174,7 +9174,7 @@
         <v>9.423070246026918e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>1.023375607422178e-08</v>
+        <v>9.42307024602692e-10</v>
       </c>
       <c r="O5" t="n">
         <v>9.42307024602692e-10</v>
@@ -9262,7 +9262,7 @@
         <v>1.509442588573122e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.023375607422178e-08</v>
+        <v>1.510362810615767e-09</v>
       </c>
       <c r="O6" t="n">
         <v>3.4571375098537e-09</v>
@@ -9350,7 +9350,7 @@
         <v>5.565025931982094e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.023375607422178e-08</v>
+        <v>5.565025931982094e-09</v>
       </c>
       <c r="O7" t="n">
         <v>5.564843868913057e-09</v>
@@ -9438,7 +9438,7 @@
         <v>8.41259954004971e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.023375607422178e-08</v>
+        <v>5.98848425911978e-09</v>
       </c>
       <c r="O8" t="n">
         <v>6.654652186780472e-09</v>
@@ -9526,7 +9526,7 @@
         <v>5.226137758719414e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>1.023375607422178e-08</v>
+        <v>5.226137758719414e-09</v>
       </c>
       <c r="O9" t="n">
         <v>5.575240588722222e-09</v>
@@ -10210,7 +10210,7 @@
         <v>8.932347048008972e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>5.989207420614343e-09</v>
+        <v>8.932347048008971e-10</v>
       </c>
       <c r="O5" t="n">
         <v>8.932347048008971e-10</v>
@@ -10298,7 +10298,7 @@
         <v>1.422382106794006e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>5.989207420614343e-09</v>
+        <v>1.42290078387383e-09</v>
       </c>
       <c r="O6" t="n">
         <v>3.225190635371609e-09</v>
@@ -10386,7 +10386,7 @@
         <v>5.16020085100906e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>5.989207420614343e-09</v>
+        <v>5.16020085100906e-09</v>
       </c>
       <c r="O7" t="n">
         <v>5.160031608904033e-09</v>
@@ -10474,7 +10474,7 @@
         <v>7.692782889637343e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>5.989207420614343e-09</v>
+        <v>5.484737596233036e-09</v>
       </c>
       <c r="O8" t="n">
         <v>6.091527615184423e-09</v>
@@ -10562,7 +10562,7 @@
         <v>4.636576871716813e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>5.989207420614343e-09</v>
+        <v>4.636576871716813e-09</v>
       </c>
       <c r="O9" t="n">
         <v>4.94352352168295e-09</v>

--- a/Results/Phase 2/Hydrogen/hydrogen human toxicity carcinogenic results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen human toxicity carcinogenic results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.677737564618071e-09</v>
+        <v>1.677737564618069e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.650950474264093e-09</v>
+        <v>1.65095047426409e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.667368806361325e-09</v>
+        <v>1.667368806361323e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.088073511496533e-09</v>
+        <v>2.088073511496535e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.65985783345613e-09</v>
+        <v>1.659857833456127e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.680465005675813e-09</v>
+        <v>1.680465005675809e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.658936865766813e-09</v>
+        <v>1.658936865766816e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.669485116694002e-09</v>
+        <v>1.669485116694e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.670226501742133e-09</v>
+        <v>1.670226501742129e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.684842750787594e-09</v>
+        <v>1.684842750787591e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.691645213931979e-09</v>
+        <v>1.691645213931977e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.704030314319009e-09</v>
+        <v>1.704030314319007e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.67118720269002e-09</v>
+        <v>1.671187202690016e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.664729222926008e-09</v>
+        <v>1.664729222926003e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.667854092329771e-09</v>
+        <v>1.667854092329768e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.657186939546875e-09</v>
+        <v>1.657186939546871e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.657672516126595e-09</v>
+        <v>1.657672516126591e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.670622176782141e-09</v>
+        <v>1.670622176782138e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.664138615587605e-09</v>
+        <v>1.6641386155876e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.699814960155807e-09</v>
+        <v>1.699814960155805e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.582338041696059e-09</v>
+        <v>1.582338041696055e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.671893161662443e-09</v>
+        <v>1.67189316166244e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.665563825889789e-09</v>
+        <v>1.665563825889782e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.669002908087009e-09</v>
+        <v>1.669002908087004e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.667543758874159e-09</v>
+        <v>1.667543758874154e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.659135760924524e-09</v>
+        <v>1.65913576092452e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.727389482115887e-09</v>
+        <v>1.727389482115884e-09</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="E3" t="n">
         <v>2.097079164580866e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.653371413735664e-09</v>
+        <v>1.653371413735662e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="V3" t="n">
         <v>1.576434241772633e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.657097077671359e-09</v>
+        <v>1.657097077671354e-09</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.336061202792217e-08</v>
+        <v>1.336061202792213e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.557967286486184e-09</v>
+        <v>6.557967286486183e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.158306107984458e-08</v>
+        <v>1.158306107984462e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.731791690728168e-09</v>
+        <v>5.731791690728163e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.495690523313495e-09</v>
+        <v>9.4956905233135e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.436799229115397e-08</v>
+        <v>1.436799229115398e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.35482517111292e-09</v>
+        <v>9.354825171112915e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.234292863145592e-08</v>
+        <v>1.234292863145591e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.279177687691604e-08</v>
+        <v>1.279177687691603e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.678676455248644e-08</v>
+        <v>1.678676455248641e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.80818793137019e-08</v>
+        <v>1.808187931370154e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.299861038443222e-08</v>
+        <v>2.299861038443228e-08</v>
       </c>
       <c r="N4" t="n">
         <v>1.245421357595173e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>9.785253999457541e-09</v>
+        <v>9.785253999457759e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.076120136136557e-08</v>
+        <v>1.076120136136551e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.367431185975967e-09</v>
+        <v>8.367431185975933e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.798040218387596e-09</v>
+        <v>8.798040218387573e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.169100907897455e-08</v>
+        <v>1.169100907897442e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.063368770531195e-08</v>
+        <v>1.063368770531196e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>2.01325857520768e-08</v>
+        <v>2.01325857520767e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.794392232997699e-09</v>
+        <v>8.794392232997634e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.246877474072478e-08</v>
+        <v>1.246877474072477e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.093805900361436e-08</v>
+        <v>1.093805900361433e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.166755279741901e-08</v>
+        <v>1.1667552797419e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.078615913715569e-08</v>
+        <v>1.078615913715572e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.795555284896582e-09</v>
+        <v>8.795555284896562e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.125246322000642e-08</v>
+        <v>3.12524632200065e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.111267452879827e-09</v>
+        <v>6.111267452879825e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>9.753405005797181e-09</v>
+        <v>9.753405005797158e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>9.753405005797181e-09</v>
+        <v>9.753405005797158e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.814074195101834e-09</v>
+        <v>7.814074195101842e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.678669917126446e-09</v>
+        <v>6.678669917126439e-09</v>
       </c>
       <c r="G5" t="n">
         <v>1.050862595375109e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.753405005797181e-09</v>
+        <v>9.753405005797158e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>9.753405005797181e-09</v>
+        <v>9.753405005797158e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>9.75313030797616e-09</v>
+        <v>9.753130307976157e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>9.753405005797181e-09</v>
+        <v>9.753405005797158e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>9.753405005797181e-09</v>
+        <v>9.753405005797158e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>9.753405005797169e-09</v>
+        <v>9.753405005797145e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.245421357595173e-08</v>
+        <v>6.930139086082352e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>7.705997075101548e-09</v>
+        <v>7.705997075101533e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>7.515815534605827e-09</v>
+        <v>7.515815534605831e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.395504295863194e-09</v>
+        <v>5.39550429586318e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>9.753405005797181e-09</v>
+        <v>9.753405005797158e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>9.753405005797181e-09</v>
+        <v>9.753405005797158e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>9.753405005797181e-09</v>
+        <v>9.753405005797158e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>7.97565605713907e-09</v>
+        <v>7.975656057139067e-09</v>
       </c>
       <c r="V5" t="n">
         <v>8.757343560404605e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>9.754120790708394e-09</v>
+        <v>9.754120790708387e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>5.729313439944909e-09</v>
+        <v>5.729313439944902e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.337457934762133e-08</v>
+        <v>1.337457934762131e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>6.043612877916212e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.753405005797181e-09</v>
+        <v>9.753405005797158e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.355792223088978e-08</v>
+        <v>1.355792223088977e-08</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.943585776606781e-09</v>
+        <v>4.943585776606778e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>5.91457133897846e-09</v>
+        <v>5.914571338978449e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>3.295907090648623e-09</v>
+        <v>3.295907090648617e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>6.205910807082058e-09</v>
+        <v>6.205910807082048e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>6.205634798090955e-09</v>
+        <v>6.20563479809094e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.245421357595173e-08</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>6.624243669308486e-09</v>
+        <v>6.624243669308479e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>6.715223889459325e-09</v>
+        <v>6.715223889459313e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.205910807082058e-09</v>
+        <v>6.205910807082048e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>7.662071326360569e-09</v>
+        <v>7.662071326360564e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.444841064026991e-09</v>
+        <v>5.44484106402698e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.205909495911967e-09</v>
+        <v>6.205909495911975e-09</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.441303038558308e-09</v>
+        <v>1.441303038558309e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.601541001541469e-09</v>
+        <v>1.601541001541466e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.505439822607024e-09</v>
+        <v>1.50543982260702e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.005286519669912e-09</v>
+        <v>2.00528651966991e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.549986045813826e-09</v>
+        <v>1.549986045813821e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.425209147465765e-09</v>
+        <v>1.42520914746576e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.555555545087869e-09</v>
+        <v>1.555555545087859e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.493359953443554e-09</v>
+        <v>1.493359953443549e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.460876582672588e-09</v>
+        <v>1.460876582672585e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.402718733264546e-09</v>
+        <v>1.402718733264542e-09</v>
       </c>
       <c r="L7" t="n">
         <v>1.360468904400315e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.292103363569833e-09</v>
+        <v>1.29210336356983e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.482316230231584e-09</v>
+        <v>1.48231623023158e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.518535468644682e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.499781067491471e-09</v>
+        <v>1.499781067491463e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.564832069106947e-09</v>
+        <v>1.564832069106943e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.562629885231629e-09</v>
+        <v>1.562629885231625e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.484184762189364e-09</v>
+        <v>1.484184762189363e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.52444837385602e-09</v>
+        <v>1.524448373856016e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.311821436170223e-09</v>
+        <v>1.31182143617022e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.454373844319521e-09</v>
+        <v>1.454373844319522e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.477548046269695e-09</v>
+        <v>1.477548046269692e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.515871442365897e-09</v>
+        <v>1.515871442365895e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.494876759693915e-09</v>
+        <v>1.494876759693911e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.502125451176004e-09</v>
+        <v>1.502125451176005e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.55293148127365e-09</v>
+        <v>1.552931481273647e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.153980325792936e-09</v>
+        <v>1.153980325792931e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.579550589126835e-09</v>
+        <v>1.579550589126831e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.625672282578284e-09</v>
+        <v>1.625672282578279e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.598364272004056e-09</v>
+        <v>1.598364272004049e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>2.046307565536246e-09</v>
+        <v>2.04630756553624e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.611121972618347e-09</v>
+        <v>1.61112197261834e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.574955258449279e-09</v>
+        <v>1.574955258449275e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.612735144847659e-09</v>
+        <v>1.612735144847656e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.594984203371095e-09</v>
+        <v>1.594984203371096e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.582640740163805e-09</v>
+        <v>1.582640740163796e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.56909979342681e-09</v>
+        <v>1.569099793426805e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.556678449795755e-09</v>
+        <v>1.556678449795754e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.537957011236864e-09</v>
+        <v>1.537957011236861e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.591661360111413e-09</v>
+        <v>1.591661360111407e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.601683249249222e-09</v>
+        <v>1.601683249249216e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.596274806361543e-09</v>
+        <v>1.59627480636154e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.615206066618931e-09</v>
+        <v>1.615206066618929e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.614689642517436e-09</v>
+        <v>1.614689642517431e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.591946522198978e-09</v>
+        <v>1.591946522198976e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.60378303262529e-09</v>
+        <v>1.603783032625287e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.542713442944608e-09</v>
+        <v>1.542713442944601e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.526800171871489e-09</v>
+        <v>1.526800171871486e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.590197780185873e-09</v>
+        <v>1.590197780185868e-09</v>
       </c>
       <c r="X8" t="n">
         <v>1.601305711766407e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.595192146441794e-09</v>
+        <v>1.595192146441786e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.597031174953502e-09</v>
+        <v>1.597031174953495e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.611740082607508e-09</v>
+        <v>1.611740082607504e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.49846975667325e-09</v>
+        <v>1.498469756673247e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1361,22 +1361,22 @@
         <v>1.469769556250399e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.468225079334209e-09</v>
+        <v>1.468225079334215e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.473908175047538e-09</v>
+        <v>1.473908175047534e-09</v>
       </c>
       <c r="E2" t="n">
         <v>1.986569751471181e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.472020811500989e-09</v>
+        <v>1.472020811500987e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.473135732749687e-09</v>
+        <v>1.473135732749686e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.471279296047181e-09</v>
+        <v>1.471279296047174e-09</v>
       </c>
       <c r="I2" t="n">
         <v>1.474338820405222e-09</v>
@@ -1385,58 +1385,58 @@
         <v>1.470068181324284e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.474319048200877e-09</v>
+        <v>1.474319048200876e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.472892768676631e-09</v>
+        <v>1.47289276867663e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.472421752916179e-09</v>
+        <v>1.472421752916177e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.468860805683946e-09</v>
+        <v>1.468860805683945e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.466339134899171e-09</v>
+        <v>1.466339134899176e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.467385462181772e-09</v>
+        <v>1.467385462181774e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.470610632415171e-09</v>
+        <v>1.470610632415174e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.476766277919092e-09</v>
+        <v>1.476766277919087e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.471751179724982e-09</v>
+        <v>1.471751179724983e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.469356751191704e-09</v>
+        <v>1.469356751191702e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.473705298110166e-09</v>
+        <v>1.473705298110165e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.354555859761017e-09</v>
+        <v>1.354555859761007e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.499946848804719e-09</v>
+        <v>1.499946848804722e-09</v>
       </c>
       <c r="X2" t="n">
         <v>1.485505864427125e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.487288096466243e-09</v>
+        <v>1.487288096466242e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.472489315075132e-09</v>
+        <v>1.47248931507514e-09</v>
       </c>
       <c r="AA2" t="n">
         <v>1.474090124332767e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.477816895685105e-09</v>
+        <v>1.477816895685104e-09</v>
       </c>
     </row>
     <row r="3">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>2.000164198230504e-09</v>
+        <v>2.000164198230502e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.467565620338237e-09</v>
+        <v>1.46756562033824e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.351142929922003e-09</v>
+        <v>1.351142929921992e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.47073443706638e-09</v>
+        <v>1.470734437066384e-09</v>
       </c>
     </row>
     <row r="4">
@@ -1534,82 +1534,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.945895898949681e-09</v>
+        <v>5.945895898949682e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>5.962410751787441e-09</v>
+        <v>5.962410751787435e-09</v>
       </c>
       <c r="D4" t="n">
         <v>7.402604665585364e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>3.567836899459458e-09</v>
+        <v>3.567836899459454e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.022808737466815e-09</v>
+        <v>7.0228087374668e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>6.721374801141826e-09</v>
+        <v>6.721374801141804e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.051375964924997e-09</v>
+        <v>7.051375964925009e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.640477179915002e-09</v>
+        <v>7.640477179915008e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.930560322311025e-09</v>
+        <v>6.930560322311015e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.318289599193245e-09</v>
+        <v>7.318289599193221e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>6.814338129558756e-09</v>
+        <v>6.814338129558764e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>7.146538385268427e-09</v>
+        <v>7.146538385268421e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>6.081681528879403e-09</v>
+        <v>6.081681528879404e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.178979815844282e-09</v>
+        <v>5.178979815844285e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>5.367578075049047e-09</v>
+        <v>5.367578075049049e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.408113411448826e-09</v>
+        <v>6.408113411448824e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.405674612475222e-09</v>
+        <v>8.405674612475212e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>6.408221938436057e-09</v>
+        <v>6.408221938436045e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>6.331116178118008e-09</v>
+        <v>6.331116178118005e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>6.946824496047497e-09</v>
+        <v>6.946824496047482e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>6.260805442670134e-09</v>
+        <v>6.260805442670112e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.380493848793431e-08</v>
+        <v>1.380493848793432e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.012035442154607e-08</v>
+        <v>1.012035442154608e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.075679216967375e-08</v>
+        <v>1.075679216967383e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.448739030896915e-09</v>
+        <v>6.44873903089691e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.346129304106981e-09</v>
+        <v>7.346129304106985e-09</v>
       </c>
       <c r="AB4" t="n">
         <v>8.855172590199707e-09</v>
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.789460773830663e-09</v>
+        <v>4.789460773830666e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>7.602647890677333e-09</v>
+        <v>7.602647890677341e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>7.602647890677333e-09</v>
+        <v>7.602647890677341e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.104708734718174e-09</v>
+        <v>6.104708734718165e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.227722448264977e-09</v>
+        <v>5.227722448264979e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>8.185980565589725e-09</v>
+        <v>8.185980565589733e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.602647890677333e-09</v>
+        <v>7.602647890677341e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.602647890677333e-09</v>
+        <v>7.602647890677341e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>7.602404320532759e-09</v>
+        <v>7.602404320532739e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>7.602647890677333e-09</v>
+        <v>7.602647890677341e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>7.602647890677333e-09</v>
+        <v>7.602647890677341e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>7.602647890677185e-09</v>
+        <v>7.602647890677175e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>6.081681528879403e-09</v>
+        <v>5.4219572392583e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>6.021229965067939e-09</v>
+        <v>6.021229965067947e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.874333739493475e-09</v>
+        <v>5.874333739493478e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.236605297420709e-09</v>
+        <v>4.236605297420728e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>7.602647890677333e-09</v>
+        <v>7.602647890677341e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>7.602647890677333e-09</v>
+        <v>7.602647890677341e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>7.602647890677333e-09</v>
+        <v>7.602647890677341e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>6.230094706662916e-09</v>
+        <v>6.230094706662896e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>6.833980983224364e-09</v>
+        <v>6.833980983224371e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>7.603200762895601e-09</v>
+        <v>7.603200762895583e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.494439486776493e-09</v>
+        <v>4.494439486776497e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.040063547121824e-08</v>
+        <v>1.040063547121825e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.737204378816495e-09</v>
+        <v>4.73720437881649e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.602647890677333e-09</v>
+        <v>7.602647890677341e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.054125706941776e-08</v>
+        <v>1.054125706941778e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.560673147133816e-09</v>
+        <v>3.560673147133815e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>4.241128185177247e-09</v>
+        <v>4.241128185177268e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.405999682990277e-09</v>
+        <v>2.405999682990268e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.445295390679015e-09</v>
+        <v>4.445295390678999e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="J6" t="n">
         <v>4.445050637743628e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.081681528879403e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>4.738458043876348e-09</v>
+        <v>4.738458043876358e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>4.802215891122491e-09</v>
+        <v>4.802215891122501e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.445295390679015e-09</v>
+        <v>4.445295390678999e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.465767952541439e-09</v>
+        <v>5.465767952541454e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.911946841500492e-09</v>
+        <v>3.911946841500499e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.445294207888213e-09</v>
+        <v>4.445294207888218e-09</v>
       </c>
     </row>
     <row r="7">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.398335508823798e-09</v>
+        <v>1.398335508823799e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.40849666365524e-09</v>
+        <v>1.408496663655241e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.375285151271752e-09</v>
+        <v>1.375285151271754e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.942095546860076e-09</v>
+        <v>1.942095546860071e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.386777092051899e-09</v>
+        <v>1.3867770920519e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.378364034901719e-09</v>
+        <v>1.37836403490172e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.391259049848191e-09</v>
+        <v>1.391259049848192e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.372955315433598e-09</v>
+        <v>1.372955315433603e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.375043471095643e-09</v>
+        <v>1.375043471095638e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.372733003286618e-09</v>
+        <v>1.372733003286615e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.380357003397695e-09</v>
+        <v>1.380357003397693e-09</v>
       </c>
       <c r="M7" t="n">
         <v>1.384339893331926e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.404550794476607e-09</v>
+        <v>1.40455079447661e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.418681389883512e-09</v>
+        <v>1.418681389883518e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.412393955281402e-09</v>
+        <v>1.412393955281401e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.394393007346641e-09</v>
+        <v>1.39439300734664e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.359005526412383e-09</v>
+        <v>1.35900552641238e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.386821732814129e-09</v>
+        <v>1.386821732814127e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.401992229447802e-09</v>
+        <v>1.401992229447801e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.37545360007519e-09</v>
+        <v>1.375453600075192e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.262539677945667e-09</v>
+        <v>1.26253967794566e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.220843298031657e-09</v>
+        <v>1.220843298031656e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.30718881477467e-09</v>
+        <v>1.307188814774679e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.295845849167269e-09</v>
+        <v>1.295845849167261e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.382259081096793e-09</v>
+        <v>1.382259081096794e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.373532898123156e-09</v>
+        <v>1.373532898123154e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.352415242824764e-09</v>
+        <v>1.352415242824768e-09</v>
       </c>
     </row>
     <row r="8">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.43682781317833e-09</v>
+        <v>1.436827813178326e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.439906694092126e-09</v>
+        <v>1.439906694092125e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.430478445832156e-09</v>
+        <v>1.430478445832157e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.960148330043826e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.433819951963216e-09</v>
+        <v>1.433819951963214e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.43110690539776e-09</v>
+        <v>1.431106905397756e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.43511774158987e-09</v>
+        <v>1.435117741589872e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.429849008458734e-09</v>
+        <v>1.429849008458735e-09</v>
       </c>
       <c r="J8" t="n">
         <v>1.427970308568307e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.429728083519043e-09</v>
+        <v>1.429728083519042e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.431770748341588e-09</v>
+        <v>1.431770748341585e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.433111960193931e-09</v>
+        <v>1.433111960193925e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.438747037390842e-09</v>
+        <v>1.438747037390847e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.442654832547746e-09</v>
+        <v>1.442654832547748e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.44084035704952e-09</v>
+        <v>1.440840357049525e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.435875038606985e-09</v>
+        <v>1.435875038606988e-09</v>
       </c>
       <c r="R8" t="n">
         <v>1.425929267512613e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.433570631876283e-09</v>
+        <v>1.433570631876289e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.438078827656831e-09</v>
+        <v>1.438078827656835e-09</v>
       </c>
       <c r="U8" t="n">
         <v>1.430352213637163e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.314241097749972e-09</v>
+        <v>1.314241097749967e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.38624558418811e-09</v>
+        <v>1.386245584188108e-09</v>
       </c>
       <c r="X8" t="n">
         <v>1.411092085095422e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.407713231635283e-09</v>
+        <v>1.407713231635284e-09</v>
       </c>
       <c r="Z8" t="n">
         <v>1.432232746154741e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.429863114350678e-09</v>
+        <v>1.429863114350677e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.423981285244268e-09</v>
+        <v>1.42398128524427e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.620693874934406e-09</v>
+        <v>1.620693874934416e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.598972094023954e-09</v>
+        <v>1.598972094023958e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.613962820647132e-09</v>
+        <v>1.613962820647136e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.060897058491482e-09</v>
+        <v>2.06089705849149e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.601339119964084e-09</v>
+        <v>1.601339119964088e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.627399308013171e-09</v>
+        <v>1.627399308013176e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.600688917657782e-09</v>
+        <v>1.600688917657784e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.607669816720469e-09</v>
+        <v>1.607669816720474e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.61654179977587e-09</v>
+        <v>1.616541799775875e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.626442995767978e-09</v>
+        <v>1.626442995767982e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.637799472394218e-09</v>
+        <v>1.637799472394239e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.646709571338797e-09</v>
+        <v>1.646709571338801e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.605973619114565e-09</v>
+        <v>1.60597361911457e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.607521498843937e-09</v>
+        <v>1.607521498843942e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.618414265285755e-09</v>
+        <v>1.618414265285762e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.602406152148475e-09</v>
+        <v>1.602406152148481e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.601705751774305e-09</v>
+        <v>1.601705751774309e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.618719025715341e-09</v>
+        <v>1.618719025715344e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.603533208142272e-09</v>
+        <v>1.603533208142277e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.640206483438956e-09</v>
+        <v>1.64020648343896e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.511626049159958e-09</v>
+        <v>1.51162604915996e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.623090341699389e-09</v>
+        <v>1.623090341699394e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.616147338215279e-09</v>
+        <v>1.616147338215287e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.615447785146119e-09</v>
+        <v>1.615447785146121e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.611882687765989e-09</v>
+        <v>1.611882687766e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.603850652687645e-09</v>
+        <v>1.603850652687652e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.672732005745352e-09</v>
+        <v>1.672732005745357e-09</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>2.070600857444349e-09</v>
+        <v>2.070600857444354e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.600278876723244e-09</v>
+        <v>1.600278876723249e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.509670715690155e-09</v>
+        <v>1.509670715690159e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.60412783827282e-09</v>
+        <v>1.604127838272824e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.127848666485581e-08</v>
+        <v>1.127848666485703e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.245364716427088e-09</v>
+        <v>6.245364716427093e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.053845730122549e-08</v>
+        <v>1.053845730122558e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.110846314488596e-09</v>
+        <v>5.110846314489225e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.048429318834285e-09</v>
+        <v>7.048429318834362e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.318650087189995e-08</v>
+        <v>1.318650087190015e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.007000745363432e-09</v>
+        <v>7.00700074536346e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.825899578697606e-09</v>
+        <v>8.825899578697641e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.164655995479981e-08</v>
+        <v>1.164655995479961e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.344238579205313e-08</v>
+        <v>1.344238579205326e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.651673913700653e-08</v>
+        <v>1.651673913701224e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.001245009811914e-08</v>
+        <v>2.001245009811878e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.093133532262108e-09</v>
+        <v>8.093133532262171e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>7.942769246701959e-09</v>
+        <v>7.942769246701962e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.080350207411789e-08</v>
+        <v>1.080350207411851e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.139737748410003e-09</v>
+        <v>7.139737748410364e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.179168465401874e-09</v>
+        <v>7.179168465401881e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.099398477176526e-08</v>
+        <v>1.099398477176562e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>7.584637322963521e-09</v>
+        <v>7.584637322963816e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.689021225864e-08</v>
+        <v>1.689021225864006e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>6.963144890609765e-09</v>
+        <v>6.963144890609787e-09</v>
       </c>
       <c r="W4" t="n">
         <v>1.26339986306278e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.102798159541319e-08</v>
+        <v>1.102798159541377e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.053826011383615e-08</v>
+        <v>1.053826011383619e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.201692223691544e-09</v>
+        <v>9.201692223691237e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.416645613233863e-09</v>
+        <v>7.416645613234321e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.85750629971564e-08</v>
+        <v>2.857506299715718e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2394,82 +2394,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.582425000793059e-09</v>
+        <v>5.582425000793052e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>8.893445095278526e-09</v>
+        <v>8.893445095278533e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>8.893445095278526e-09</v>
+        <v>8.893445095278533e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>7.130424563856985e-09</v>
+        <v>7.130424563856983e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>6.098243234860008e-09</v>
+        <v>6.098243234860002e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>9.580006681193583e-09</v>
+        <v>9.580006681193572e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>8.893445095278526e-09</v>
+        <v>8.893445095278533e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>8.893445095278526e-09</v>
+        <v>8.893445095278533e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>8.893117314685085e-09</v>
+        <v>8.893117314685078e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>8.893445095278526e-09</v>
+        <v>8.893445095278533e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>8.893445095278526e-09</v>
+        <v>8.893445095278533e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>8.893445095278384e-09</v>
+        <v>8.893445095278381e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>8.093133532262108e-09</v>
+        <v>6.326850600576623e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>7.032173053328819e-09</v>
+        <v>7.032173053328812e-09</v>
       </c>
       <c r="P5" t="n">
         <v>6.859281477153471e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.93173398176201e-09</v>
+        <v>4.931733981762001e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>8.893445095278526e-09</v>
+        <v>8.893445095278528e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>8.893445095278526e-09</v>
+        <v>8.893445095278533e-09</v>
       </c>
       <c r="T5" t="n">
         <v>8.893445095278526e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>7.277238032159117e-09</v>
+        <v>7.27723803215911e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>7.987455596437429e-09</v>
+        <v>7.987455596437428e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>8.894095806058799e-09</v>
+        <v>8.894095806058791e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>5.235195552799915e-09</v>
+        <v>5.2351955527999e-09</v>
       </c>
       <c r="Y5" t="n">
         <v>1.218527349741427e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.520921102620973e-09</v>
+        <v>5.520921102620971e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.893445095278526e-09</v>
+        <v>8.893445095278533e-09</v>
       </c>
       <c r="AB5" t="n">
         <v>1.235208244738942e-08</v>
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.349290865298727e-09</v>
+        <v>4.349290865298731e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>5.195495171600673e-09</v>
+        <v>5.195495171600683e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.913355200041072e-09</v>
+        <v>2.913355200041075e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>5.449394634227911e-09</v>
+        <v>5.449394634227929e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>5.449065630606565e-09</v>
+        <v>5.44906563060657e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>8.093133532262108e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>5.813967582788569e-09</v>
+        <v>5.81396758278859e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>5.893255944081888e-09</v>
+        <v>5.893255944081898e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.449394634227911e-09</v>
+        <v>5.449394634227929e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>6.718007591449114e-09</v>
+        <v>6.718007591449126e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.786129886607723e-09</v>
+        <v>4.786129886607727e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.44939341120002e-09</v>
+        <v>5.44939341120003e-09</v>
       </c>
     </row>
     <row r="7">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.416381641658412e-09</v>
+        <v>1.416381641658381e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.546514817629376e-09</v>
+        <v>1.546514817629382e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.458778254880795e-09</v>
+        <v>1.4587782548808e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.984277179654479e-09</v>
+        <v>1.984277179654459e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.533095475532956e-09</v>
+        <v>1.53309547553296e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.376619544276596e-09</v>
+        <v>1.376619544276598e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.537022058246623e-09</v>
+        <v>1.537022058246627e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.495852176416183e-09</v>
+        <v>1.495852176416187e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.415204812469985e-09</v>
+        <v>1.415204812469987e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.385358753525708e-09</v>
+        <v>1.385358753525713e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.316465675308136e-09</v>
+        <v>1.316465675308175e-09</v>
       </c>
       <c r="M7" t="n">
         <v>1.26826161429846e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.505137374624294e-09</v>
+        <v>1.505137374624302e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.494621556020172e-09</v>
+        <v>1.494621556020176e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.429588989543649e-09</v>
+        <v>1.429588989543654e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.526260191300911e-09</v>
+        <v>1.526260191300914e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.530884162269544e-09</v>
+        <v>1.530884162269549e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.428689203347727e-09</v>
+        <v>1.428689203347708e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.51992685937332e-09</v>
+        <v>1.519926859373316e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.301929542330641e-09</v>
+        <v>1.301929542330645e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41609705751133e-09</v>
+        <v>1.416097057511333e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.403766643805952e-09</v>
+        <v>1.403766643805955e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.445824859921694e-09</v>
+        <v>1.445824859921685e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.4491316304111e-09</v>
+        <v>1.449131630411104e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.468956647099138e-09</v>
+        <v>1.468956647099142e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.517394194761156e-09</v>
+        <v>1.517394194761155e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.114646289713148e-09</v>
+        <v>1.114646289713142e-09</v>
       </c>
     </row>
     <row r="8">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.535268757163222e-09</v>
+        <v>1.535268757163231e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.572757986029384e-09</v>
+        <v>1.572757986029389e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.547828297002123e-09</v>
+        <v>1.547828297002126e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>2.021619509999856e-09</v>
+        <v>2.021619509999855e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.569019168550737e-09</v>
+        <v>1.56901916855074e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.523882309218976e-09</v>
+        <v>1.52388230921898e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.570155573892432e-09</v>
+        <v>1.570155573892435e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.558404045521639e-09</v>
+        <v>1.558404045521642e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.532332510744591e-09</v>
+        <v>1.532332510744594e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.526902365032334e-09</v>
+        <v>1.526902365032338e-09</v>
       </c>
       <c r="L8" t="n">
         <v>1.506912271520366e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.493889369088316e-09</v>
+        <v>1.493889369088318e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.560932642690597e-09</v>
+        <v>1.560932642690601e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.557695791443165e-09</v>
+        <v>1.55769579144317e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.538998532891675e-09</v>
+        <v>1.538998532891678e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.566976124626791e-09</v>
+        <v>1.566976124626793e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.568379645779068e-09</v>
+        <v>1.568379645779071e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.538893887734666e-09</v>
+        <v>1.538893887734669e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.565221494410402e-09</v>
+        <v>1.565221494410404e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.502705295736438e-09</v>
+        <v>1.502705295736441e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.469049736487039e-09</v>
+        <v>1.469049736487041e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.531925359703721e-09</v>
+        <v>1.531925359703724e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.544118978583857e-09</v>
+        <v>1.544118978583854e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.544924016625429e-09</v>
+        <v>1.544924016625434e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.550379365016937e-09</v>
+        <v>1.550379365016945e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.564386568486116e-09</v>
+        <v>1.564386568486121e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.45001634126556e-09</v>
+        <v>1.450016341265562e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.586703096053681e-09</v>
+        <v>1.586703096053683e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.568891698683405e-09</v>
+        <v>1.568891698683408e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.589560035716747e-09</v>
+        <v>1.589560035716749e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.048159739144875e-09</v>
+        <v>2.04815973914488e-09</v>
       </c>
       <c r="F2" t="n">
         <v>1.5737154924165e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.595751186784024e-09</v>
+        <v>1.595751186784028e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.569241145298912e-09</v>
+        <v>1.569241145298913e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.581032947537233e-09</v>
+        <v>1.581032947537235e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.585905201516892e-09</v>
+        <v>1.585905201516891e-09</v>
       </c>
       <c r="K2" t="n">
         <v>1.579164404339307e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.603717692526163e-09</v>
+        <v>1.603717692526165e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.612006682625063e-09</v>
+        <v>1.612006682625064e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.570165424230638e-09</v>
+        <v>1.570165424230635e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.574579238250533e-09</v>
+        <v>1.574579238250529e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.587965960924794e-09</v>
+        <v>1.587965960924798e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.575918212897156e-09</v>
+        <v>1.575918212897157e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.569406324423421e-09</v>
+        <v>1.569406324423414e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.588376434985752e-09</v>
+        <v>1.588376434985751e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.571585798427121e-09</v>
+        <v>1.571585798427123e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.601115014982667e-09</v>
+        <v>1.60111501498267e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.478403595178168e-09</v>
+        <v>1.478403595178175e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.594033386404336e-09</v>
+        <v>1.594033386404337e-09</v>
       </c>
       <c r="X2" t="n">
         <v>1.59381170365995e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.599702737348915e-09</v>
+        <v>1.599702737348914e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.582643253816929e-09</v>
+        <v>1.582643253816931e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.573952124695141e-09</v>
+        <v>1.57395212469514e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.637908854055969e-09</v>
+        <v>1.63790885405597e-09</v>
       </c>
     </row>
     <row r="3">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="E3" t="n">
         <v>2.056084024298421e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5703161305172e-09</v>
+        <v>1.570316130517199e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.473348151013622e-09</v>
+        <v>1.473348151013625e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.574014299738819e-09</v>
+        <v>1.57401429973882e-09</v>
       </c>
     </row>
     <row r="4">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.584353061317994e-09</v>
+        <v>9.584353061318024e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>5.714953282594591e-09</v>
+        <v>5.714953282594605e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.115800408654521e-08</v>
+        <v>1.115800408654522e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.166287345724121e-09</v>
+        <v>5.166287345724097e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.066044565365318e-09</v>
+        <v>7.066044565365328e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.17049211298631e-08</v>
+        <v>1.170492112986315e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.036407416634446e-09</v>
+        <v>6.036407416634426e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>9.020281559342302e-09</v>
+        <v>9.020281559342282e-09</v>
       </c>
       <c r="J4" t="n">
         <v>1.055543199862852e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.102835981634444e-09</v>
+        <v>8.102835981634472e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.423036855760798e-08</v>
+        <v>1.423036855760799e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.732515063739531e-08</v>
+        <v>1.732515063739533e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.959213087288708e-09</v>
+        <v>5.959213087288711e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>6.644986338138347e-09</v>
+        <v>6.644986338138388e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>9.81812773727103e-09</v>
+        <v>9.818127737271073e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.407227155074723e-09</v>
+        <v>7.407227155074727e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>5.972588609244582e-09</v>
+        <v>5.972588609244581e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.003034977279696e-08</v>
+        <v>1.003034977279695e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.462731166875284e-09</v>
+        <v>6.46273116687532e-09</v>
       </c>
       <c r="U4" t="n">
         <v>1.33169980249029e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>7.042720126419954e-09</v>
+        <v>7.042720126420297e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.192855288782877e-08</v>
+        <v>1.192855288782876e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.214311471326488e-08</v>
+        <v>1.21431147132649e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33226437141509e-08</v>
+        <v>1.332264371415099e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.420764170295169e-09</v>
+        <v>8.420764170295187e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.853620295327883e-09</v>
+        <v>6.853620295327901e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.526838342418683e-08</v>
+        <v>2.526838342418688e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.122875390115644e-09</v>
+        <v>5.122875390115651e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>8.140865623134439e-09</v>
+        <v>8.140865623134442e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>8.140865623134439e-09</v>
+        <v>8.140865623134442e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.533874849116804e-09</v>
+        <v>6.533874849116799e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.593042996471024e-09</v>
+        <v>5.593042996471018e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>8.766665558357446e-09</v>
+        <v>8.766665558357472e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>8.140865623134439e-09</v>
+        <v>8.140865623134442e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>8.140865623134439e-09</v>
+        <v>8.140865623134442e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>8.140553725412014e-09</v>
+        <v>8.140553725412006e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>8.140865623134439e-09</v>
+        <v>8.140865623134442e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>8.140865623134439e-09</v>
+        <v>8.140865623134448e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>8.140865623134253e-09</v>
+        <v>8.140865623134267e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.959213087288708e-09</v>
+        <v>5.801418293880623e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>6.444318733248284e-09</v>
+        <v>6.444318733248317e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>6.286728300884501e-09</v>
+        <v>6.286728300884521e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.52977142696044e-09</v>
+        <v>4.529771426960441e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>8.140865623134439e-09</v>
+        <v>8.140865623134442e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>8.140865623134439e-09</v>
+        <v>8.140865623134442e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>8.140865623134439e-09</v>
+        <v>8.140865623134442e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>6.667982474680746e-09</v>
+        <v>6.667982474680738e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>7.31539275308158e-09</v>
+        <v>7.315392753081586e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>8.141458745086582e-09</v>
+        <v>8.141458745086588e-09</v>
       </c>
       <c r="X5" t="n">
         <v>4.806376228896107e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.114185423156284e-08</v>
+        <v>1.114185423156286e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.06681467206766e-09</v>
+        <v>5.066814672067664e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.140865623134439e-09</v>
+        <v>8.140865623134442e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.129340878212505e-08</v>
+        <v>1.129340878212504e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.899803506149304e-09</v>
+        <v>3.899803506149292e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>4.650042278586879e-09</v>
+        <v>4.650042278586892e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.62671306832088e-09</v>
+        <v>2.6267130683209e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.875147752224152e-09</v>
+        <v>4.875147752224172e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>4.874834711749942e-09</v>
+        <v>4.874834711749906e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.875146609472355e-09</v>
+        <v>4.875146609472383e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>5.959213087288708e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>5.198375558269527e-09</v>
+        <v>5.198375558269503e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>5.268672060428952e-09</v>
+        <v>5.268672060428934e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.875147752224152e-09</v>
+        <v>4.875147752224172e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.999887419592708e-09</v>
+        <v>5.999887419592753e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>4.875146609472355e-09</v>
+        <v>4.875146609472383e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.287101902835492e-09</v>
+        <v>4.287101902835532e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.875146609472352e-09</v>
+        <v>4.875146609472386e-09</v>
       </c>
     </row>
     <row r="7">
@@ -3342,25 +3342,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.412331151567309e-09</v>
+        <v>1.412331151567311e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.519160668596615e-09</v>
+        <v>1.519160668596616e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.398164114030602e-09</v>
+        <v>1.398164114030606e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.960799857343349e-09</v>
+        <v>1.960799857343348e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.491404230856946e-09</v>
+        <v>1.491404230856948e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.35862542886823e-09</v>
+        <v>1.358625428868233e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.517601464374353e-09</v>
+        <v>1.517601464374357e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.448356828959258e-09</v>
@@ -3369,7 +3369,7 @@
         <v>1.392375568732e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.458887117388975e-09</v>
+        <v>1.458887117388977e-09</v>
       </c>
       <c r="L7" t="n">
         <v>1.312789529123878e-09</v>
@@ -3378,46 +3378,46 @@
         <v>1.267867395152745e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.511484438178625e-09</v>
+        <v>1.511484438178622e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.484354851066834e-09</v>
+        <v>1.484354851066837e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.404473597421432e-09</v>
+        <v>1.404473597421433e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.477813181600018e-09</v>
+        <v>1.47781318160002e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.516462726717415e-09</v>
+        <v>1.516462726717413e-09</v>
       </c>
       <c r="S7" t="n">
         <v>1.402921511148905e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.503496893988739e-09</v>
+        <v>1.50349689398874e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.327925841709768e-09</v>
+        <v>1.32792584170977e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.365002594396756e-09</v>
+        <v>1.365002594396747e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.370389976674066e-09</v>
+        <v>1.370389976674067e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.373061338719292e-09</v>
+        <v>1.373061338719294e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.337320537554606e-09</v>
+        <v>1.337320537554607e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.436642008589453e-09</v>
+        <v>1.436642008589459e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.488983071791853e-09</v>
+        <v>1.488983071791856e-09</v>
       </c>
       <c r="AB7" t="n">
         <v>1.115062799416361e-09</v>
@@ -3430,16 +3430,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.513136748382022e-09</v>
+        <v>1.513136748382023e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.543933121705552e-09</v>
+        <v>1.543933121705554e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.50954764081822e-09</v>
+        <v>1.509547640818225e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>2.004805139527691e-09</v>
+        <v>2.004805139527693e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.536127647812578e-09</v>
@@ -3448,67 +3448,67 @@
         <v>1.497748564134301e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.54357312543104e-09</v>
+        <v>1.543573125431042e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.523858397885932e-09</v>
+        <v>1.523858397885935e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5049416788417e-09</v>
+        <v>1.504941678841706e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.526781169481565e-09</v>
+        <v>1.526781169481566e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.484859589422416e-09</v>
+        <v>1.48485958942242e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.472708865406103e-09</v>
+        <v>1.472708865406101e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.541714137949905e-09</v>
+        <v>1.54171413794991e-09</v>
       </c>
       <c r="O8" t="n">
         <v>1.533783903377067e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.510824401076222e-09</v>
+        <v>1.510824401076226e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.532146397569229e-09</v>
+        <v>1.53214639756923e-09</v>
       </c>
       <c r="R8" t="n">
         <v>1.543220175292699e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.510528670936975e-09</v>
+        <v>1.51052867093698e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.539500154085194e-09</v>
+        <v>1.539500154085193e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.489143982342066e-09</v>
+        <v>1.489143982342065e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.429106021640692e-09</v>
+        <v>1.429106021640689e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.501383670497657e-09</v>
+        <v>1.501383670497659e-09</v>
       </c>
       <c r="X8" t="n">
         <v>1.502377465996975e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.492006321256833e-09</v>
+        <v>1.492006321256834e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.520138423564451e-09</v>
+        <v>1.520138423564452e-09</v>
       </c>
       <c r="AA8" t="n">
         <v>1.535262645000826e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.4290844588176e-09</v>
+        <v>1.429084458817601e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3674,19 +3674,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.566083222700435e-09</v>
+        <v>1.566083222700434e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.549941307929058e-09</v>
+        <v>1.549941307929061e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.567134094019672e-09</v>
+        <v>1.567134094019674e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.034707716299629e-09</v>
+        <v>2.034707716299628e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.557804379990989e-09</v>
+        <v>1.557804379990994e-09</v>
       </c>
       <c r="G2" t="n">
         <v>1.575069045925843e-09</v>
@@ -3695,64 +3695,64 @@
         <v>1.552219755465519e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.561198482007017e-09</v>
+        <v>1.56119848200702e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.567074115857985e-09</v>
+        <v>1.567074115857984e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.560794379603676e-09</v>
+        <v>1.560794379603679e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.580507892291115e-09</v>
+        <v>1.580507892291112e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.588397667798795e-09</v>
+        <v>1.588397667798797e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.549512365952896e-09</v>
+        <v>1.5495123659529e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.555314822150378e-09</v>
+        <v>1.555314822150385e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.568111570828012e-09</v>
+        <v>1.568111570828017e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.557289087877062e-09</v>
+        <v>1.557289087877063e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.555570265473108e-09</v>
+        <v>1.555570265473113e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.569829304167305e-09</v>
+        <v>1.569829304167312e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.556031573776301e-09</v>
+        <v>1.556031573776306e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.585097869264079e-09</v>
+        <v>1.585097869264083e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.466014906585785e-09</v>
+        <v>1.466014906585787e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.576294292757726e-09</v>
+        <v>1.57629429275773e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.579760370731429e-09</v>
+        <v>1.579760370731435e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.600191058503782e-09</v>
+        <v>1.600191058503779e-09</v>
       </c>
       <c r="Z2" t="n">
         <v>1.564557189880077e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.557077813621373e-09</v>
+        <v>1.557077813621378e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.615330851299475e-09</v>
+        <v>1.615330851299476e-09</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>2.044962465245284e-09</v>
+        <v>2.044962465245286e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="J3" t="n">
         <v>1.552599006170873e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="V3" t="n">
         <v>1.454466781765543e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.555938659571469e-09</v>
+        <v>1.555938659571471e-09</v>
       </c>
     </row>
     <row r="4">
@@ -3850,85 +3850,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.767316064401308e-09</v>
+        <v>8.767316064401304e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>5.417381484833748e-09</v>
+        <v>5.417381484833752e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.744239864104113e-09</v>
+        <v>9.744239864104189e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.476970247811917e-09</v>
+        <v>4.476970247811916e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.515762976718254e-09</v>
+        <v>7.51576297671825e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.081733066557355e-08</v>
+        <v>1.081733066557335e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.238483995792957e-09</v>
+        <v>6.238483995792976e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.411658258142416e-09</v>
+        <v>8.411658258142419e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.008231488795135e-08</v>
+        <v>1.008231488795139e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.952261657749174e-09</v>
+        <v>7.952261657749199e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.255792844843538e-08</v>
+        <v>1.255792844843541e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.531423334339806e-08</v>
+        <v>1.531423334339803e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.211624513522319e-09</v>
+        <v>5.211624513522332e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>6.301659937743016e-09</v>
+        <v>6.301659937743044e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>9.167635270237202e-09</v>
+        <v>9.167635270237189e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.113514981216396e-09</v>
+        <v>7.113514981216401e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.035281788734038e-09</v>
+        <v>7.035281788734037e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>9.764775308514299e-09</v>
+        <v>9.764775308514266e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.046960367981267e-09</v>
+        <v>7.046960367981268e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.342280697169021e-08</v>
+        <v>1.34228069716902e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.377626432646029e-09</v>
+        <v>8.377626432646077e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.194320298385539e-08</v>
+        <v>1.19432029838554e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.282948876301745e-08</v>
+        <v>1.282948876301747e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.816559924662985e-08</v>
+        <v>1.816559924662971e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.129270701740921e-09</v>
+        <v>8.129270701740929e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.084291141925338e-09</v>
+        <v>7.084291141925345e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.362736246872738e-08</v>
+        <v>2.362736246872741e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.060934593680614e-09</v>
+        <v>5.060934593680609e-09</v>
       </c>
       <c r="C5" t="n">
+        <v>8.036282372285706e-09</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8.036282372285706e-09</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.451997447373762e-09</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.524459004009025e-09</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.653240116794677e-09</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.036282372285706e-09</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8.036282372285706e-09</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.036036434740338e-09</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.036282372285706e-09</v>
+      </c>
+      <c r="L5" t="n">
         <v>8.036282372285711e-09</v>
       </c>
-      <c r="D5" t="n">
-        <v>8.036282372285711e-09</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6.451997447373747e-09</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5.524459004009018e-09</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.65324011679467e-09</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8.036282372285711e-09</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8.036282372285711e-09</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8.036036434740332e-09</v>
-      </c>
-      <c r="K5" t="n">
-        <v>8.036282372285711e-09</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8.036282372285715e-09</v>
-      </c>
       <c r="M5" t="n">
-        <v>8.036282372285594e-09</v>
+        <v>8.036282372285589e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.211624513522319e-09</v>
+        <v>5.729890079124571e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>6.363706707551369e-09</v>
+        <v>6.363706707551371e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>6.208342936745968e-09</v>
+        <v>6.208342936745964e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.476210846089861e-09</v>
+        <v>4.476210846089876e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>8.036282372285711e-09</v>
+        <v>8.036282372285706e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>8.036282372285711e-09</v>
+        <v>8.036282372285706e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>8.036282372285711e-09</v>
+        <v>8.036282372285706e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>6.584641284301304e-09</v>
+        <v>6.584641284301307e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>7.223356465067014e-09</v>
+        <v>7.223356465067015e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>8.036867113753567e-09</v>
+        <v>8.036867113753569e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.748907382334212e-09</v>
+        <v>4.748907382334218e-09</v>
       </c>
       <c r="Y5" t="n">
         <v>1.099560619240389e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.005665981117981e-09</v>
+        <v>5.00566598111798e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.036282372285711e-09</v>
+        <v>8.036282372285706e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.114428192191803e-08</v>
+        <v>1.114428192191802e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.772250655824542e-09</v>
+        <v>3.772250655824559e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>4.494255310581937e-09</v>
+        <v>4.494255310581939e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.547071078591028e-09</v>
+        <v>2.547071078591038e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.710889275325486e-09</v>
+        <v>4.710889275325506e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>4.710642198649437e-09</v>
+        <v>4.710642198649445e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.710888136194805e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>5.211624513522319e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>5.021952884786169e-09</v>
+        <v>5.021952884786175e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>5.089603882890905e-09</v>
+        <v>5.089603882890921e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.710889275325486e-09</v>
+        <v>4.710889275325506e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.793690621897511e-09</v>
+        <v>5.793690621897542e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>4.710888136194805e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.144973654769232e-09</v>
+        <v>4.144973654769239e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.710888136194804e-09</v>
+        <v>4.710888136194817e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.411243320933051e-09</v>
+        <v>1.411243320933059e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.508040048705037e-09</v>
+        <v>1.508040048705038e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.407393577978972e-09</v>
+        <v>1.407393577978973e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.96466811003463e-09</v>
+        <v>1.964668110034634e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.462525809240122e-09</v>
+        <v>1.462525809240126e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.357898383922032e-09</v>
+        <v>1.357898383922043e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.495202887131119e-09</v>
+        <v>1.495202887131121e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.442383926607468e-09</v>
+        <v>1.442383926607473e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.38325660997041e-09</v>
+        <v>1.383256609970407e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4443639603545e-09</v>
+        <v>1.444363960354498e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.326906270729432e-09</v>
+        <v>1.326906270729433e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2838967970182e-09</v>
+        <v>1.283896797018202e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.510400800445569e-09</v>
+        <v>1.510400800445573e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.475212896853162e-09</v>
+        <v>1.475212896853165e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.39885638724828e-09</v>
+        <v>1.398856387248282e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.46481564492022e-09</v>
+        <v>1.464815644920218e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.475467316835196e-09</v>
+        <v>1.4754673168352e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.389488173486063e-09</v>
+        <v>1.389488173486064e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.472483273233148e-09</v>
+        <v>1.472483273233145e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.29951046318977e-09</v>
+        <v>1.299510463189772e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.30960230549567e-09</v>
+        <v>1.309602305495671e-09</v>
       </c>
       <c r="W7" t="n">
         <v>1.35216501790596e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.333215350877436e-09</v>
+        <v>1.33321535087744e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.211691778739576e-09</v>
+        <v>1.211691778739579e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.420477977153766e-09</v>
+        <v>1.420477977153768e-09</v>
       </c>
       <c r="AA7" t="n">
         <v>1.465658449271812e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.125176523589036e-09</v>
+        <v>1.125176523589039e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.500246382503264e-09</v>
+        <v>1.500246382503271e-09</v>
       </c>
       <c r="C8" t="n">
         <v>1.528147287341019e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.499545608509998e-09</v>
+        <v>1.49954560851e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.998173528795852e-09</v>
+        <v>1.998173528795849e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.515301235401137e-09</v>
+        <v>1.515301235401141e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.484960089388435e-09</v>
+        <v>1.484960089388441e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.524584785451735e-09</v>
+        <v>1.524584785451737e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.509530716630934e-09</v>
+        <v>1.509530716630937e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.490022785924576e-09</v>
+        <v>1.490022785924574e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.510027535892484e-09</v>
+        <v>1.510027535892486e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.476297425485071e-09</v>
+        <v>1.476297425485069e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.46461775339108e-09</v>
+        <v>1.464617753391083e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.528792494930075e-09</v>
+        <v>1.528792494930072e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.518584342855813e-09</v>
+        <v>1.518584342855816e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.496638636329464e-09</v>
+        <v>1.496638636329466e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.515827825818926e-09</v>
+        <v>1.515827825818923e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.518955548081155e-09</v>
+        <v>1.518955548081156e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.494093802552222e-09</v>
+        <v>1.494093802552226e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.518059107035827e-09</v>
+        <v>1.518059107035831e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.468422222722233e-09</v>
+        <v>1.468422222722236e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.400101108227298e-09</v>
+        <v>1.400101108227299e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.483576636411854e-09</v>
+        <v>1.483576636411857e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.478420555498582e-09</v>
+        <v>1.478420555498583e-09</v>
       </c>
       <c r="Y8" t="n">
         <v>1.443557630675549e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.502922147692441e-09</v>
+        <v>1.50292214769244e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.516000030229078e-09</v>
+        <v>1.516000030229075e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.419332706669991e-09</v>
+        <v>1.419332706669994e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.467260950915138e-09</v>
+        <v>1.467260950915141e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.460996418889379e-09</v>
+        <v>1.460996418889378e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.477439760901289e-09</v>
+        <v>1.4774397609013e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>1.985723360196679e-09</v>
+        <v>1.985723360196691e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.465591322867256e-09</v>
+        <v>1.465591322867267e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.470963616147923e-09</v>
+        <v>1.470963616147922e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.470065370768681e-09</v>
+        <v>1.470065370768679e-09</v>
       </c>
       <c r="I2" t="n">
         <v>1.467985883775478e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.467581865523946e-09</v>
+        <v>1.467581865523954e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.480538081923254e-09</v>
+        <v>1.480538081923249e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.477937852512874e-09</v>
+        <v>1.477937852512875e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.481511110926997e-09</v>
+        <v>1.481511110926999e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.474061651956732e-09</v>
+        <v>1.474061651956733e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.464023996104117e-09</v>
+        <v>1.464023996104118e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.468846368908905e-09</v>
+        <v>1.468846368908908e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.469058700957717e-09</v>
+        <v>1.469058700957714e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.467288856953422e-09</v>
+        <v>1.46728885695342e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.470535519986884e-09</v>
+        <v>1.470535519986887e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.466004882283626e-09</v>
+        <v>1.46600488228362e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.477967679913629e-09</v>
+        <v>1.477967679913627e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.345246022307279e-09</v>
+        <v>1.345246022307277e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.479524437805238e-09</v>
+        <v>1.47952443780525e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.469898718915975e-09</v>
+        <v>1.469898718915972e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.466489822087793e-09</v>
+        <v>1.466489822087789e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.469711504397535e-09</v>
+        <v>1.469711504397532e-09</v>
       </c>
       <c r="AA2" t="n">
         <v>1.465895240929289e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.483408064983391e-09</v>
+        <v>1.483408064983389e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>1.998693269747239e-09</v>
+        <v>1.998693269747261e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.463830706192763e-09</v>
+        <v>1.463830706192762e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.345267412922792e-09</v>
+        <v>1.345267412922789e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.467197961456313e-09</v>
+        <v>1.467197961456305e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4622,85 +4622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.647211502292289e-09</v>
+        <v>6.647211502292335e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>5.429072701793573e-09</v>
+        <v>5.429072701793552e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.003443530396764e-08</v>
+        <v>1.003443530396778e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.005408393164423e-09</v>
+        <v>4.005408393164406e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>6.787621394118179e-09</v>
+        <v>6.787621394118176e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.514589760288e-09</v>
+        <v>7.514589760288068e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>8.282750204810385e-09</v>
+        <v>8.2827502048104e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.458964315223463e-09</v>
+        <v>7.458964315223456e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.657655259424247e-09</v>
+        <v>7.657655259424285e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.040614628035297e-08</v>
+        <v>1.040614628035302e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.314614437656981e-09</v>
+        <v>9.314614437656974e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>1.083683248993402e-08</v>
+        <v>1.083683248993398e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.802507646656727e-09</v>
+        <v>8.802507646656715e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.866879162867421e-09</v>
+        <v>5.866879162867448e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.048523998733606e-09</v>
+        <v>7.048523998733687e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.453667159440113e-09</v>
+        <v>7.453667159440107e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.34752939015725e-09</v>
+        <v>7.347529390157215e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.251177944910916e-09</v>
+        <v>7.251177944910953e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>6.826200388076503e-09</v>
+        <v>6.826200388076492e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>9.581558301614105e-09</v>
+        <v>9.58155830161412e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>5.888639529780766e-09</v>
+        <v>5.888639529780759e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02968252876654e-08</v>
+        <v>1.029682528766541e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>7.852390446783987e-09</v>
+        <v>7.85239044678434e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.780932861615396e-09</v>
+        <v>6.780932861615391e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.194954211826853e-09</v>
+        <v>7.194954211826834e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.608422713251183e-09</v>
+        <v>6.608422713251176e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.205600418017003e-08</v>
+        <v>1.205600418017002e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.113434414410478e-09</v>
+        <v>5.113434414410502e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>8.135077721474014e-09</v>
+        <v>8.135077721474048e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>8.135077721474014e-09</v>
+        <v>8.135077721474048e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.526141793287331e-09</v>
+        <v>6.526141793287327e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.584171127007479e-09</v>
+        <v>5.584171127007495e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>8.761635145397774e-09</v>
+        <v>8.76163514539776e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>8.135077721474014e-09</v>
+        <v>8.135077721474048e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>8.135077721474014e-09</v>
+        <v>8.135077721474048e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>8.134791717182624e-09</v>
+        <v>8.13479171718261e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>8.135077721474014e-09</v>
+        <v>8.135077721474048e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>8.135077721474014e-09</v>
+        <v>8.135077721474048e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>8.135077721473805e-09</v>
+        <v>8.13507772147384e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>8.802507646656727e-09</v>
+        <v>5.792798648689303e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>6.436477275765319e-09</v>
+        <v>6.436477275765327e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>6.27869609079057e-09</v>
+        <v>6.278696090790585e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.519612538829114e-09</v>
+        <v>4.519612538829123e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>8.135077721474014e-09</v>
+        <v>8.135077721474048e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>8.135077721474014e-09</v>
+        <v>8.135077721474048e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>8.135077721474014e-09</v>
+        <v>8.135077721474048e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>6.660694748467908e-09</v>
+        <v>6.660694748467926e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>7.309070340949998e-09</v>
+        <v>7.309070340949996e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>8.135671561357072e-09</v>
+        <v>8.135671561357098e-09</v>
       </c>
       <c r="X5" t="n">
         <v>4.796552152258207e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.114018295762125e-08</v>
+        <v>1.114018295762126e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.057305838637162e-09</v>
+        <v>5.057305838637148e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.135077721474014e-09</v>
+        <v>8.135077721474048e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.129143682176632e-08</v>
+        <v>1.129143682176629e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.005902546789878e-09</v>
+        <v>4.005902546789868e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>4.781942878993548e-09</v>
+        <v>4.781942878993566e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.689029089173501e-09</v>
+        <v>2.689029089173511e-09</v>
       </c>
       <c r="G6" t="n">
         <v>5.014789984422109e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>5.014502737237477e-09</v>
+        <v>5.014502737237493e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>8.802507646656727e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>5.349133960228509e-09</v>
+        <v>5.349133960228547e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>5.421848038589627e-09</v>
+        <v>5.421848038589652e-09</v>
       </c>
       <c r="Q6" t="n">
         <v>5.014789984422109e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>6.178389334558747e-09</v>
+        <v>6.178389334558743e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.406520573301272e-09</v>
+        <v>4.406520573301308e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.014788741528949e-09</v>
+        <v>5.014788741528935e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.388121285000403e-09</v>
+        <v>1.388121285000395e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.426057752227659e-09</v>
+        <v>1.42605775222765e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.329793329282642e-09</v>
+        <v>1.329793329282654e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.936162867203262e-09</v>
+        <v>1.936162867203284e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.399552637350142e-09</v>
+        <v>1.399552637350137e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.366152812213083e-09</v>
+        <v>1.366152812213077e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.373659754197169e-09</v>
+        <v>1.373659754197172e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.385332568107618e-09</v>
+        <v>1.385332568107628e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.363171856918914e-09</v>
+        <v>1.36317185691892e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.311417557610654e-09</v>
+        <v>1.311417557610662e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.325528551276889e-09</v>
+        <v>1.325528551276883e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.306576042985757e-09</v>
+        <v>1.306576042985753e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.349062320628143e-09</v>
+        <v>1.349062320628139e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.407307664483869e-09</v>
+        <v>1.40730766448387e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.378504470437953e-09</v>
+        <v>1.378504470437962e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.378646883007753e-09</v>
+        <v>1.378646883007746e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.389579473736149e-09</v>
+        <v>1.389579473736167e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.368959946639209e-09</v>
+        <v>1.368959946639205e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.396821505153578e-09</v>
+        <v>1.396821505153579e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.325205759960741e-09</v>
+        <v>1.325205759960755e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.276616581941019e-09</v>
+        <v>1.276616581941013e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.316408962618242e-09</v>
+        <v>1.316408962618235e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.373870198331031e-09</v>
+        <v>1.373870198331032e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.393466249762555e-09</v>
+        <v>1.393466249762562e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.373652040723044e-09</v>
+        <v>1.373652040723035e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.396910118087875e-09</v>
+        <v>1.396910118087874e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.294871690199191e-09</v>
+        <v>1.294871690199179e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.431280811125285e-09</v>
+        <v>1.431280811125286e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.44227749258427e-09</v>
+        <v>1.442277492584271e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.414920215379705e-09</v>
+        <v>1.414920215379706e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.957271827766597e-09</v>
+        <v>1.957271827766612e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.434812484826099e-09</v>
+        <v>1.434812484826105e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.424987751230472e-09</v>
+        <v>1.424987751230471e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.427505188377196e-09</v>
+        <v>1.427505188377192e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.430736868912296e-09</v>
+        <v>1.4307368689123e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.421781768323635e-09</v>
+        <v>1.421781768323636e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.409657501730776e-09</v>
+        <v>1.409657501730789e-09</v>
       </c>
       <c r="L8" t="n">
         <v>1.413477819407614e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.408427626151219e-09</v>
+        <v>1.408427626151214e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.420309558903969e-09</v>
+        <v>1.420309558903972e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4367737201226e-09</v>
+        <v>1.436773720122609e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.428490547846166e-09</v>
+        <v>1.428490547846178e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.42876767806807e-09</v>
+        <v>1.428767678068078e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.431972197685315e-09</v>
+        <v>1.431972197685314e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.425836910179135e-09</v>
+        <v>1.425836910179131e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.433983370389438e-09</v>
+        <v>1.43398337038942e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.413360775730847e-09</v>
+        <v>1.413360775730857e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.314009675433352e-09</v>
+        <v>1.31400967543335e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.410914962797892e-09</v>
+        <v>1.4109149627979e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.427434289276046e-09</v>
+        <v>1.427434289276038e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.432941658298112e-09</v>
+        <v>1.432941658298113e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.427147812350733e-09</v>
+        <v>1.427147812350732e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.433914048202589e-09</v>
+        <v>1.433914048202588e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.404999062390157e-09</v>
+        <v>1.404999062390155e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5218,85 +5218,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.421947148283584e-09</v>
+        <v>1.421947148283582e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.416847328646692e-09</v>
+        <v>1.41684732864669e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.425598240918633e-09</v>
+        <v>1.425598240918632e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>1.959803983479916e-09</v>
+        <v>1.959803983479915e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.422189547720075e-09</v>
+        <v>1.422189547720073e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.418753473936551e-09</v>
+        <v>1.418753473936549e-09</v>
       </c>
       <c r="H2" t="n">
         <v>1.42104968252105e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.42319314955423e-09</v>
+        <v>1.423193149554229e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.417349315038184e-09</v>
+        <v>1.417349315038181e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.421740691966747e-09</v>
+        <v>1.421740691966746e-09</v>
       </c>
       <c r="L2" t="n">
         <v>1.422898273686748e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.421506939802769e-09</v>
+        <v>1.421506939802768e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.419370428630902e-09</v>
+        <v>1.419370428630899e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.417047917055359e-09</v>
+        <v>1.417047917055357e-09</v>
       </c>
       <c r="P2" t="n">
         <v>1.415557490052316e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.418347175339263e-09</v>
+        <v>1.418347175339261e-09</v>
       </c>
       <c r="R2" t="n">
         <v>1.423123784945716e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.421408215547845e-09</v>
+        <v>1.421408215547846e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.418436609751409e-09</v>
+        <v>1.418436609751406e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.418385380012879e-09</v>
+        <v>1.418385380012878e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.288775116685362e-09</v>
+        <v>1.288775116685363e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.432919105427384e-09</v>
+        <v>1.432919105427382e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.431803297830837e-09</v>
+        <v>1.431803297830835e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.425331995903171e-09</v>
+        <v>1.42533199590317e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.421395794395647e-09</v>
+        <v>1.421395794395645e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.421154405160295e-09</v>
+        <v>1.421154405160293e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.422637639617211e-09</v>
+        <v>1.422637639617209e-09</v>
       </c>
     </row>
     <row r="3">
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>1.974019007188001e-09</v>
+        <v>1.974019007187999e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="J3" t="n">
         <v>1.415862967880707e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.286449732599823e-09</v>
+        <v>1.286449732599813e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.419040208881103e-09</v>
+        <v>1.419040208881101e-09</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.720848907055545e-09</v>
+        <v>6.720848907055556e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>5.884428580754174e-09</v>
+        <v>5.884428580754172e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.037766409003623e-09</v>
+        <v>8.037766409003612e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>3.346154672132966e-09</v>
+        <v>3.34615467213296e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.294275746720467e-09</v>
+        <v>7.294275746720461e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>5.959071763257404e-09</v>
+        <v>5.959071763257408e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.273547733617109e-09</v>
+        <v>7.273547733617104e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.595590660037984e-09</v>
+        <v>7.595590660037966e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.453281004329741e-09</v>
+        <v>6.453281004329765e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>6.98399056854429e-09</v>
+        <v>6.983990568544279e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>6.845852164509281e-09</v>
+        <v>6.845852164509256e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>7.004710066621285e-09</v>
+        <v>7.004710066621277e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>6.359728943950644e-09</v>
+        <v>6.359728943950634e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.570048176485411e-09</v>
+        <v>5.570048176485413e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>5.195240454345844e-09</v>
+        <v>5.195240454345846e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.999372499974702e-09</v>
+        <v>5.999372499974696e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.676471700353142e-09</v>
+        <v>7.676471700353129e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>6.428782737909555e-09</v>
+        <v>6.428782737909551e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>6.312010142142745e-09</v>
+        <v>6.312010142142732e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>5.971323392652215e-09</v>
+        <v>5.971323392652211e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>5.798952521824445e-09</v>
+        <v>5.798952521824537e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>9.537150647034403e-09</v>
+        <v>9.537150647034379e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>9.422359534768939e-09</v>
+        <v>9.422359534769037e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.924390309678406e-09</v>
+        <v>7.924390309678413e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.48475410329238e-09</v>
+        <v>6.484754103292367e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.848373681164349e-09</v>
+        <v>6.848373681164353e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.552134964201137e-09</v>
+        <v>7.552134964201132e-09</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.641640330988137e-09</v>
+        <v>4.641640330988124e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>7.364703814538012e-09</v>
+        <v>7.364703814537989e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>7.364703814538012e-09</v>
+        <v>7.364703814537989e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.914752834832386e-09</v>
+        <v>5.914752834832361e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.06586179664966e-09</v>
+        <v>5.065861796649643e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>7.929348766984168e-09</v>
+        <v>7.929348766984134e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.364703814538012e-09</v>
+        <v>7.364703814537989e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.364703814538012e-09</v>
+        <v>7.364703814537989e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>7.364431559199353e-09</v>
+        <v>7.364431559199324e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>7.364703814538012e-09</v>
+        <v>7.364703814537989e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>7.364703814538012e-09</v>
+        <v>7.364703814537989e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>7.36470381453799e-09</v>
+        <v>7.364703814537961e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>6.359728943950644e-09</v>
+        <v>5.253874056274478e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>5.833948402043005e-09</v>
+        <v>5.833948402042973e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.691758163315494e-09</v>
+        <v>5.691758163315474e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.106496205497562e-09</v>
+        <v>4.10649620549755e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>7.364703814538012e-09</v>
+        <v>7.364703814537989e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>7.364703814538012e-09</v>
+        <v>7.364703814537989e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>7.364703814538012e-09</v>
+        <v>7.364703814537989e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>6.036129217194421e-09</v>
+        <v>6.0361292171944e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>6.620467344726442e-09</v>
+        <v>6.620467344726414e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>7.365238974860795e-09</v>
+        <v>7.365238974860775e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.356070384771647e-09</v>
+        <v>4.356070384771632e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.007306717053122e-08</v>
+        <v>1.007306717053118e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.591058028733591e-09</v>
+        <v>4.591058028733578e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.364703814538012e-09</v>
+        <v>7.364703814537989e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.020917132226648e-08</v>
+        <v>1.020917132226646e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.552062833377392e-09</v>
+        <v>3.552062833377387e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>4.231958380019726e-09</v>
+        <v>4.231958380019711e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.398338777847446e-09</v>
+        <v>2.398338777847438e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.435957712863513e-09</v>
+        <v>4.4359577128635e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>4.435684284225255e-09</v>
+        <v>4.43568428422523e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.359728943950644e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>4.728879318564061e-09</v>
+        <v>4.728879318564051e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>4.792584742115346e-09</v>
+        <v>4.792584742115333e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.435957712863513e-09</v>
+        <v>4.4359577128635e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.455399770855137e-09</v>
+        <v>5.455399770855108e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.903047699532881e-09</v>
+        <v>3.903047699532874e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.43595653956391e-09</v>
+        <v>4.435956539563903e-09</v>
       </c>
     </row>
     <row r="7">
@@ -5658,85 +5658,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.327211401792531e-09</v>
+        <v>1.327211401792529e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.35849926896502e-09</v>
+        <v>1.358499268965019e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.307315952488132e-09</v>
+        <v>1.30731595248813e-09</v>
       </c>
       <c r="E7" t="n">
         <v>1.920841132738781e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.327755032652557e-09</v>
+        <v>1.327755032652556e-09</v>
       </c>
       <c r="G7" t="n">
         <v>1.346254720668037e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.334568313712851e-09</v>
+        <v>1.334568313712849e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.321595894722897e-09</v>
+        <v>1.321595894722896e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.332835211737132e-09</v>
+        <v>1.332835211737133e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.329778602857019e-09</v>
+        <v>1.329778602857018e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.322195820914594e-09</v>
+        <v>1.322195820914592e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.33163269136733e-09</v>
+        <v>1.331632691367328e-09</v>
       </c>
       <c r="N7" t="n">
         <v>1.343456500964327e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.356283852099022e-09</v>
+        <v>1.356283852099021e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.365108359632298e-09</v>
+        <v>1.365108359632297e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.349599308853009e-09</v>
+        <v>1.349599308853008e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.322212986222063e-09</v>
+        <v>1.322212986222061e-09</v>
       </c>
       <c r="S7" t="n">
         <v>1.330706524919714e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.349313024018643e-09</v>
+        <v>1.349313024018642e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.348800442127329e-09</v>
+        <v>1.348800442127328e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.209074653719278e-09</v>
+        <v>1.209074653719268e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.263222703859337e-09</v>
+        <v>1.263222703859335e-09</v>
       </c>
       <c r="X7" t="n">
         <v>1.270821869608346e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.30818895883227e-09</v>
+        <v>1.308188958832267e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.330595349855824e-09</v>
+        <v>1.330595349855823e-09</v>
       </c>
       <c r="AA7" t="n">
         <v>1.332732661554239e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.324677838448279e-09</v>
+        <v>1.324677838448278e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5746,34 +5746,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.380164748417239e-09</v>
+        <v>1.380164748417238e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.389301008052346e-09</v>
+        <v>1.389301008052344e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.374763348215752e-09</v>
+        <v>1.374763348215749e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.93560788113769e-09</v>
+        <v>1.935607881137689e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.380654501627492e-09</v>
+        <v>1.380654501627491e-09</v>
       </c>
       <c r="G8" t="n">
         <v>1.385635844846017e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.382614701023539e-09</v>
+        <v>1.382614701023537e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.378855676075642e-09</v>
+        <v>1.37885567607564e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.379571421399098e-09</v>
+        <v>1.379571421399095e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.381126376765929e-09</v>
+        <v>1.381126376765927e-09</v>
       </c>
       <c r="L8" t="n">
         <v>1.378833768537234e-09</v>
@@ -5782,10 +5782,10 @@
         <v>1.381736240782771e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.384979600657786e-09</v>
+        <v>1.384979600657782e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.388493574726869e-09</v>
+        <v>1.388493574726868e-09</v>
       </c>
       <c r="P8" t="n">
         <v>1.391018326773503e-09</v>
@@ -5794,37 +5794,37 @@
         <v>1.386751344531462e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.379067090065804e-09</v>
+        <v>1.379067090065801e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.381216107842667e-09</v>
+        <v>1.381216107842666e-09</v>
       </c>
       <c r="T8" t="n">
         <v>1.386710518431636e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.386426062299056e-09</v>
+        <v>1.386426062299055e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.253569209214968e-09</v>
+        <v>1.25356920921497e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.362021644081555e-09</v>
+        <v>1.362021644081554e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.364363481117912e-09</v>
+        <v>1.364363481117911e-09</v>
       </c>
       <c r="Y8" t="n">
         <v>1.374894323868978e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.381153101682103e-09</v>
+        <v>1.381153101682102e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.381884196080739e-09</v>
+        <v>1.381884196080737e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.379702460355244e-09</v>
+        <v>1.379702460355243e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5990,85 +5990,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.421259319455218e-09</v>
+        <v>1.421259319455217e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.413965706797735e-09</v>
+        <v>1.413965706797733e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.422132769743467e-09</v>
+        <v>1.422132769743466e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>1.96240490159102e-09</v>
+        <v>1.962404901591018e-09</v>
       </c>
       <c r="F2" t="n">
         <v>1.416614024122565e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.419160703715507e-09</v>
+        <v>1.419160703715506e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.416205381884714e-09</v>
+        <v>1.416205381884711e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.419007490863861e-09</v>
+        <v>1.41900749086386e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.415271288188064e-09</v>
+        <v>1.415271288188062e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.416720735904265e-09</v>
+        <v>1.416720735904261e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.417502911993383e-09</v>
+        <v>1.417502911993384e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.416034535282488e-09</v>
+        <v>1.416034535282485e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.415112424518763e-09</v>
+        <v>1.415112424518762e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.413106464231634e-09</v>
+        <v>1.41310646423163e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.412433565026319e-09</v>
+        <v>1.412433565026316e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.413986669768866e-09</v>
+        <v>1.413986669768862e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.421274791864874e-09</v>
+        <v>1.421274791864876e-09</v>
       </c>
       <c r="S2" t="n">
         <v>1.416655354464353e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.414727378933375e-09</v>
+        <v>1.414727378933372e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.415601412450153e-09</v>
+        <v>1.415601412450152e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.284800217351739e-09</v>
+        <v>1.284800217351737e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.452611494656115e-09</v>
+        <v>1.452611494656116e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.43063290687074e-09</v>
+        <v>1.430632906870741e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.423698638479841e-09</v>
+        <v>1.423698638479839e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.416646186796705e-09</v>
+        <v>1.416646186796703e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.417673140267442e-09</v>
+        <v>1.41767314026744e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.421627816861465e-09</v>
+        <v>1.421627816861463e-09</v>
       </c>
     </row>
     <row r="3">
@@ -6078,85 +6078,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>1.973256806775746e-09</v>
+        <v>1.973256806775745e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.411673409284385e-09</v>
+        <v>1.411673409284383e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.280918530452623e-09</v>
+        <v>1.280918530452625e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.414895086749237e-09</v>
+        <v>1.414895086749231e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6166,85 +6166,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.472283734665963e-09</v>
+        <v>7.472283734665962e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>6.167560234496452e-09</v>
+        <v>6.16756023449645e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.235015989770124e-09</v>
+        <v>8.235015989770126e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.132716766607388e-09</v>
+        <v>4.132716766607387e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>6.971394154371338e-09</v>
+        <v>6.971394154371343e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>6.955667864619878e-09</v>
+        <v>6.955667864619887e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.039938940679034e-09</v>
+        <v>7.03993894067903e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.580303636585479e-09</v>
+        <v>7.580303636585474e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.985439586136321e-09</v>
+        <v>6.985439586136374e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>6.809044798307352e-09</v>
+        <v>6.80904479830736e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>6.658983625022268e-09</v>
+        <v>6.658983625022276e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>6.785890087581346e-09</v>
+        <v>6.785890087581352e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>6.352317272197171e-09</v>
+        <v>6.352317272197166e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.586140202508289e-09</v>
+        <v>5.586140202508287e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>5.393037043938166e-09</v>
+        <v>5.393037043938163e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.020879902818318e-09</v>
+        <v>6.020879902818335e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.281383581028447e-09</v>
+        <v>8.281383581028444e-09</v>
       </c>
       <c r="S4" t="n">
         <v>6.390067845169306e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>6.419209811891787e-09</v>
+        <v>6.419209811891789e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>6.25869134295117e-09</v>
+        <v>6.258691342951172e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>6.137813178934933e-09</v>
+        <v>6.137813178934947e-09</v>
       </c>
       <c r="W4" t="n">
         <v>1.536304917396677e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.002334221966412e-08</v>
+        <v>1.002334221966418e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.573786979117876e-09</v>
+        <v>8.573786979117908e-09</v>
       </c>
       <c r="Z4" t="n">
         <v>6.282902852709584e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.993211594996606e-09</v>
+        <v>6.993211594996614e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.488031501638238e-09</v>
+        <v>8.488031501638239e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6254,85 +6254,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.614611736488978e-09</v>
+        <v>4.614611736488974e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>7.319471411720491e-09</v>
+        <v>7.3194714117205e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>7.319471411720491e-09</v>
+        <v>7.3194714117205e-09</v>
       </c>
       <c r="E5" t="n">
         <v>5.879213422969642e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.035997261564766e-09</v>
+        <v>5.035997261564781e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>7.880341685923495e-09</v>
+        <v>7.880341685923498e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.319471411720491e-09</v>
+        <v>7.3194714117205e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.319471411720491e-09</v>
+        <v>7.3194714117205e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>7.319186947095422e-09</v>
+        <v>7.319186947095427e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>7.319471411720491e-09</v>
+        <v>7.3194714117205e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>7.319471411720491e-09</v>
+        <v>7.3194714117205e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>7.319471411720619e-09</v>
+        <v>7.31947141172062e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>6.352317272197169e-09</v>
+        <v>5.222752650329519e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>5.798949171623546e-09</v>
+        <v>5.798949171623533e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.657709481377159e-09</v>
+        <v>5.65770948137715e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.083045074819991e-09</v>
+        <v>4.083045074819998e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>7.319471411720491e-09</v>
+        <v>7.3194714117205e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>7.319471411720491e-09</v>
+        <v>7.3194714117205e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>7.319471411720491e-09</v>
+        <v>7.3194714117205e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>5.999833417882726e-09</v>
+        <v>5.999833417882731e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>6.580189302979295e-09</v>
+        <v>6.580189302979306e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>7.320002994453856e-09</v>
+        <v>7.320002994453843e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.330950838878117e-09</v>
+        <v>4.330950838878119e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.000982335267269e-08</v>
+        <v>1.000982335267268e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.56436757932161e-09</v>
+        <v>4.564367579321608e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.319471411720491e-09</v>
+        <v>7.3194714117205e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.014492351946426e-08</v>
+        <v>1.014492351946427e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.466427218143799e-09</v>
+        <v>3.46642721814379e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>4.127760838517358e-09</v>
+        <v>4.127760838517346e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.344201149266364e-09</v>
+        <v>2.344201149266367e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.32619075618577e-09</v>
+        <v>4.32619075618578e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>4.325905117356851e-09</v>
+        <v>4.325905117356857e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>6.352317272197171e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>4.611115266929035e-09</v>
+        <v>4.611115266929051e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>4.673081459534157e-09</v>
+        <v>4.673081459534153e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.32619075618577e-09</v>
+        <v>4.32619075618578e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.31770790867573e-09</v>
+        <v>5.317707908675739e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="Z6" t="n">
         <v>3.807829795903349e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.32618958198193e-09</v>
+        <v>4.326189581981928e-09</v>
       </c>
     </row>
     <row r="7">
@@ -6433,82 +6433,82 @@
         <v>1.303112268476992e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.347549797477196e-09</v>
+        <v>1.347549797477197e-09</v>
       </c>
       <c r="D7" t="n">
         <v>1.299794275753594e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.900505399466128e-09</v>
+        <v>1.900505399466127e-09</v>
       </c>
       <c r="F7" t="n">
         <v>1.33254920464212e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.315655605904036e-09</v>
+        <v>1.315655605904032e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.335091458613007e-09</v>
+        <v>1.335091458613006e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.318291157470114e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.316865840616178e-09</v>
+        <v>1.316865840616175e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.331370496418725e-09</v>
+        <v>1.331370496418726e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.326052068117186e-09</v>
+        <v>1.326052068117185e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.335834880635023e-09</v>
+        <v>1.335834880635019e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.340582478035185e-09</v>
+        <v>1.340582478035184e-09</v>
       </c>
       <c r="O7" t="n">
         <v>1.351540444510653e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.355491186996294e-09</v>
+        <v>1.355491186996293e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.347325103609946e-09</v>
+        <v>1.347325103609947e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305273339760858e-09</v>
+        <v>1.305273339760859e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.330777905527258e-09</v>
+        <v>1.330777905527261e-09</v>
       </c>
       <c r="T7" t="n">
         <v>1.343220412400689e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.337211126007709e-09</v>
+        <v>1.337211126007706e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.195040092515379e-09</v>
+        <v>1.195040092515377e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.118998314845305e-09</v>
+        <v>1.118998314845303e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.249840508235031e-09</v>
+        <v>1.249840508235029e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.289851545966275e-09</v>
+        <v>1.289851545966276e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.330655775295328e-09</v>
+        <v>1.330655775295327e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.325281288375464e-09</v>
+        <v>1.325281288375462e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.302776184153041e-09</v>
+        <v>1.302776184153037e-09</v>
       </c>
     </row>
     <row r="8">
@@ -6518,85 +6518,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.370397780910647e-09</v>
+        <v>1.370397780910643e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.383323385562254e-09</v>
+        <v>1.383323385562253e-09</v>
       </c>
       <c r="D8" t="n">
         <v>1.369761533935932e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.929302779420159e-09</v>
+        <v>1.929302779420162e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>1.379146385343078e-09</v>
+        <v>1.379146385343074e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.374006423673483e-09</v>
+        <v>1.37400642367348e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.379894476763655e-09</v>
+        <v>1.379894476763656e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.37505239518341e-09</v>
+        <v>1.375052395183406e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.372133542310235e-09</v>
+        <v>1.372133542310233e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.37871678112681e-09</v>
+        <v>1.378716781126807e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.377079055389908e-09</v>
+        <v>1.377079055389902e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.380061889550594e-09</v>
+        <v>1.380061889550591e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.381299950733638e-09</v>
+        <v>1.381299950733639e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.384279900113814e-09</v>
+        <v>1.384279900113812e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.38540460132973e-09</v>
+        <v>1.385404601329732e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.383242112107727e-09</v>
+        <v>1.383242112107729e-09</v>
       </c>
       <c r="R8" t="n">
         <v>1.371396547641386e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.378381768942807e-09</v>
+        <v>1.378381768942806e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.382115173691148e-09</v>
+        <v>1.38211517369115e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.380254962748668e-09</v>
+        <v>1.380254962748665e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24572525441195e-09</v>
+        <v>1.245725254411947e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.317977520472765e-09</v>
+        <v>1.317977520472764e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.355532547649047e-09</v>
+        <v>1.355532547649049e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.366803428933477e-09</v>
+        <v>1.366803428933476e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.378317031630424e-09</v>
+        <v>1.37831703163042e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.376898576425145e-09</v>
+        <v>1.376898576425144e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.370613358878454e-09</v>
+        <v>1.370613358878452e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6762,16 +6762,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.526788599124574e-09</v>
+        <v>1.526788599124582e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.513534799773588e-09</v>
+        <v>1.513534799773587e-09</v>
       </c>
       <c r="D2" t="n">
         <v>1.526016482146329e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.015318454434801e-09</v>
+        <v>2.01531845443481e-09</v>
       </c>
       <c r="F2" t="n">
         <v>1.518527653513226e-09</v>
@@ -6780,25 +6780,25 @@
         <v>1.54145356286901e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.516967254248899e-09</v>
+        <v>1.516967254248898e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.525808046863643e-09</v>
+        <v>1.525808046863642e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.529873938231976e-09</v>
+        <v>1.529873938231979e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>1.537414265129296e-09</v>
+        <v>1.537414265129292e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.54956638043481e-09</v>
+        <v>1.549566380434814e-09</v>
       </c>
       <c r="M2" t="n">
         <v>1.561829665748212e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.529584309160131e-09</v>
+        <v>1.529584309160132e-09</v>
       </c>
       <c r="O2" t="n">
         <v>1.519897798281947e-09</v>
@@ -6807,40 +6807,40 @@
         <v>1.529528171978529e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.519734291187557e-09</v>
+        <v>1.519734291187558e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.519049497294909e-09</v>
+        <v>1.519049497294908e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.526899173261532e-09</v>
+        <v>1.526899173261527e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.521347443459583e-09</v>
+        <v>1.52134744345958e-09</v>
       </c>
       <c r="U2" t="n">
         <v>1.54683573858653e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.405651650041159e-09</v>
+        <v>1.40565165004116e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.529994961439619e-09</v>
+        <v>1.52999496143962e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>1.53502856710062e-09</v>
+        <v>1.535028567100622e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.528903187322834e-09</v>
+        <v>1.528903187322835e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.525593716406825e-09</v>
+        <v>1.52559371640683e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.517911840478903e-09</v>
+        <v>1.517911840478904e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.577704971784121e-09</v>
+        <v>1.577704971784119e-09</v>
       </c>
     </row>
     <row r="3">
@@ -6859,7 +6859,7 @@
         <v>1.518746446597815e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>2.026430065595607e-09</v>
+        <v>2.02643006559561e-09</v>
       </c>
       <c r="F3" t="n">
         <v>1.518746446597815e-09</v>
@@ -6874,7 +6874,7 @@
         <v>1.518746446597815e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.514892353971169e-09</v>
+        <v>1.514892353971168e-09</v>
       </c>
       <c r="K3" t="n">
         <v>1.518746446597815e-09</v>
@@ -6910,7 +6910,7 @@
         <v>1.518746446597815e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.404296352999366e-09</v>
+        <v>1.404296352999368e-09</v>
       </c>
       <c r="W3" t="n">
         <v>1.518746446597815e-09</v>
@@ -6938,85 +6938,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.813609427164148e-09</v>
+        <v>8.813609427165323e-09</v>
       </c>
       <c r="C4" t="n">
         <v>5.893569596239324e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.45773087135274e-09</v>
+        <v>9.457730871352783e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.590359594742079e-09</v>
+        <v>4.590359594742508e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.395027348312757e-09</v>
+        <v>7.395027348312756e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.241089638862274e-08</v>
+        <v>1.241089638862281e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.131826597643351e-09</v>
+        <v>7.131826597643333e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>9.443716010956547e-09</v>
+        <v>9.443716010956569e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.074708415443807e-08</v>
+        <v>1.074708415443847e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.192328647368521e-08</v>
+        <v>1.192328647368528e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.504832767709736e-08</v>
+        <v>1.504832767710188e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8656971007186e-08</v>
+        <v>1.865697100718596e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.023375607422183e-08</v>
+        <v>1.02337560742218e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>7.085853425377566e-09</v>
+        <v>7.085853425377639e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>9.58319370527721e-09</v>
+        <v>9.583193705277402e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.480348981124326e-09</v>
+        <v>7.48034898112446e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.614844606810498e-09</v>
+        <v>7.614844606810554e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>8.758334206103958e-09</v>
+        <v>8.7583342061048e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>8.14008401071558e-09</v>
+        <v>8.14008401071579e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.439093405268606e-08</v>
+        <v>1.439093405268617e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>6.439893823628577e-09</v>
+        <v>6.439893823628598e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01969702665151e-08</v>
+        <v>1.019697026651491e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.186671040153785e-08</v>
+        <v>1.186671040154047e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.880100408722825e-09</v>
+        <v>9.88010040872285e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.55545131202055e-09</v>
+        <v>8.55545131202079e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.928773857833569e-09</v>
+        <v>6.928773857833679e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.52458133018053e-08</v>
+        <v>2.524581330180531e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7026,82 +7026,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.285383915195284e-09</v>
+        <v>5.285383915195294e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>8.412599540049816e-09</v>
+        <v>8.412599540049826e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>8.412599540049816e-09</v>
+        <v>8.412599540049826e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.747449466822365e-09</v>
+        <v>6.74744946682236e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.772567561057415e-09</v>
+        <v>5.772567561057425e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>9.061048071809383e-09</v>
+        <v>9.0610480718094e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>8.412599540049816e-09</v>
+        <v>8.412599540049826e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>8.412599540049816e-09</v>
+        <v>8.412599540049826e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>8.412229991405977e-09</v>
+        <v>8.41222999140599e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>8.412599540049816e-09</v>
+        <v>8.412599540049826e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>8.412599540049816e-09</v>
+        <v>8.412599540049826e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>8.412599540049708e-09</v>
+        <v>8.412599540049726e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.023375607422183e-08</v>
+        <v>5.988484259119795e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>6.654652186780468e-09</v>
+        <v>6.654652186780478e-09</v>
       </c>
       <c r="P5" t="n">
         <v>6.491358330813262e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.670814669589663e-09</v>
+        <v>4.670814669589672e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>8.412599540049816e-09</v>
+        <v>8.412599540049826e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>8.412599540049816e-09</v>
+        <v>8.412599540049822e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>8.412599540049816e-09</v>
+        <v>8.412599540049826e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>6.886280825577387e-09</v>
+        <v>6.886280825577409e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>7.556761070147337e-09</v>
+        <v>7.556761070147341e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>8.413214127945684e-09</v>
+        <v>8.413214127945696e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.957430195736672e-09</v>
+        <v>4.957430195736677e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.152197615319611e-08</v>
+        <v>1.152197615319613e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.227294279415454e-09</v>
+        <v>5.227294279415465e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.412599540049816e-09</v>
+        <v>8.412599540049826e-09</v>
       </c>
       <c r="AB5" t="n">
         <v>1.16792377541144e-08</v>
@@ -7114,85 +7114,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.172720061113514e-09</v>
+        <v>4.172720061113524e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>4.983014166268218e-09</v>
+        <v>4.983014166268228e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.797720907511375e-09</v>
+        <v>2.79772090751138e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>5.226138948707436e-09</v>
+        <v>5.226138948707449e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>5.225768210075583e-09</v>
+        <v>5.225768210075595e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.023375607422183e-08</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>5.575240588722215e-09</v>
+        <v>5.575240588722227e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>5.651164205849771e-09</v>
+        <v>5.651164205849767e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.226138948707436e-09</v>
+        <v>5.226138948707449e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>5.226137758719405e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>6.440599196213709e-09</v>
+        <v>6.440599196213729e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.591021033150786e-09</v>
+        <v>4.591021033150795e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.226137758719403e-09</v>
+        <v>5.226137758719413e-09</v>
       </c>
     </row>
     <row r="7">
@@ -7202,82 +7202,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.388405383766271e-09</v>
+        <v>1.388405383766273e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>1.468060546175429e-09</v>
+        <v>1.468060546175428e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>1.395012743045391e-09</v>
+        <v>1.395012743045389e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.951315985037725e-09</v>
+        <v>1.951315985037745e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.439293477852277e-09</v>
+        <v>1.439293477852276e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.301285057749114e-09</v>
+        <v>1.301285057749112e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>1.448531342798757e-09</v>
+        <v>1.448531342798759e-09</v>
       </c>
       <c r="I7" t="n">
         <v>1.396472326877608e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.344036763924015e-09</v>
+        <v>1.344036763924016e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.327973050048143e-09</v>
+        <v>1.327973050048141e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.254596003113351e-09</v>
+        <v>1.25459600311333e-09</v>
       </c>
       <c r="M7" t="n">
         <v>1.186520430498841e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.373481340331236e-09</v>
+        <v>1.373481340331237e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.429296957505206e-09</v>
+        <v>1.429296957505202e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.371807275979563e-09</v>
+        <v>1.371807275979564e-09</v>
       </c>
       <c r="Q7" t="n">
         <v>1.431575586657524e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.436168659513245e-09</v>
+        <v>1.436168659513242e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.388167406716969e-09</v>
+        <v>1.388167406716955e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>1.422426290921315e-09</v>
+        <v>1.422426290921314e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.270486662050766e-09</v>
+        <v>1.270486662050764e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.322847878311086e-09</v>
+        <v>1.322847878311089e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.370554813640345e-09</v>
+        <v>1.370554813640344e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.342048997988506e-09</v>
+        <v>1.342048997988476e-09</v>
       </c>
       <c r="Y7" t="n">
         <v>1.377235400858014e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.395656252577523e-09</v>
+        <v>1.395656252577512e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.441936387015808e-09</v>
+        <v>1.441936387015805e-09</v>
       </c>
       <c r="AB7" t="n">
         <v>1.092341760060338e-09</v>
@@ -7290,85 +7290,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.467483000163915e-09</v>
+        <v>1.467483000163907e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.490472553555018e-09</v>
+        <v>1.490472553555019e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.469717252714059e-09</v>
+        <v>1.46971725271406e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>1.981141308406605e-09</v>
+        <v>1.981141308406606e-09</v>
       </c>
       <c r="F8" t="n">
         <v>1.482376299532419e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.442507937934522e-09</v>
+        <v>1.442507937934523e-09</v>
       </c>
       <c r="H8" t="n">
         <v>1.485019158258068e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>1.470172932726451e-09</v>
+        <v>1.47017293272645e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.452134100276063e-09</v>
+        <v>1.452134100276065e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.450611761740451e-09</v>
+        <v>1.450611761740452e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.429377086851839e-09</v>
+        <v>1.42937708685186e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.410665769681685e-09</v>
+        <v>1.410665769681686e-09</v>
       </c>
       <c r="N8" t="n">
         <v>1.463488222876412e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.479197995686202e-09</v>
+        <v>1.479197995686203e-09</v>
       </c>
       <c r="P8" t="n">
         <v>1.462670381079874e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.480071272117678e-09</v>
+        <v>1.48007127211768e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.481476341011637e-09</v>
+        <v>1.481476341011636e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.46748529398503e-09</v>
+        <v>1.467485293985029e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.477521465672651e-09</v>
+        <v>1.47752146567265e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.433876745460634e-09</v>
+        <v>1.433876745460632e-09</v>
       </c>
       <c r="V8" t="n">
         <v>1.368592334497104e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.462567296185257e-09</v>
+        <v>1.462567296185255e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.45463066488202e-09</v>
+        <v>1.454630664882017e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.464515210542279e-09</v>
+        <v>1.464515210542281e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.469587285862421e-09</v>
+        <v>1.46958728586242e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.482963018589955e-09</v>
+        <v>1.482963018589953e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38368948053846e-09</v>
+        <v>1.383689480538459e-09</v>
       </c>
     </row>
   </sheetData>
@@ -7534,25 +7534,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.485280903847016e-09</v>
+        <v>1.485280903847017e-09</v>
       </c>
       <c r="C2" t="n">
         <v>1.484361395867707e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.489957557463517e-09</v>
+        <v>1.489957557463516e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>1.996803385149892e-09</v>
+        <v>1.996803385149893e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.486885907059384e-09</v>
+        <v>1.486885907059385e-09</v>
       </c>
       <c r="G2" t="n">
         <v>1.502883371103062e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.484049817449849e-09</v>
+        <v>1.48404981744985e-09</v>
       </c>
       <c r="I2" t="n">
         <v>1.489124049397686e-09</v>
@@ -7567,13 +7567,13 @@
         <v>1.498059839704865e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.493196332561957e-09</v>
+        <v>1.493196332561956e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.483924332037448e-09</v>
+        <v>1.483924332037446e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.481980550253201e-09</v>
+        <v>1.481980550253202e-09</v>
       </c>
       <c r="P2" t="n">
         <v>1.490494124156686e-09</v>
@@ -7582,37 +7582,37 @@
         <v>1.48941335282161e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.488835433947198e-09</v>
+        <v>1.488835433947199e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.488514034652014e-09</v>
+        <v>1.488514034652015e-09</v>
       </c>
       <c r="T2" t="n">
         <v>1.485048359589344e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.488940743766737e-09</v>
+        <v>1.488940743766735e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.368361031559468e-09</v>
+        <v>1.368361031559467e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.498111793516453e-09</v>
+        <v>1.498111793516452e-09</v>
       </c>
       <c r="X2" t="n">
         <v>1.499826458256332e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.508489377391217e-09</v>
+        <v>1.508489377391216e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.486938177925879e-09</v>
+        <v>1.486938177925878e-09</v>
       </c>
       <c r="AA2" t="n">
         <v>1.486353996241947e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.524875135209104e-09</v>
+        <v>1.524875135209105e-09</v>
       </c>
     </row>
     <row r="3">
@@ -7622,85 +7622,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>2.009717693100911e-09</v>
+        <v>2.00971769310091e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.482771603938309e-09</v>
+        <v>1.482771603938308e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>1.367515435947712e-09</v>
+        <v>1.367515435947714e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.486399666946395e-09</v>
+        <v>1.486399666946394e-09</v>
       </c>
     </row>
     <row r="4">
@@ -7710,85 +7710,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.997219927768413e-09</v>
+        <v>5.997219927768416e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>6.152305946709152e-09</v>
+        <v>6.152305946709156e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.627401206773315e-09</v>
+        <v>7.627401206773322e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>3.774347767482911e-09</v>
+        <v>3.774347767482914e-09</v>
       </c>
       <c r="F4" t="n">
         <v>6.890082406896205e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>9.83522584519284e-09</v>
+        <v>9.835225845192828e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>6.360555980364008e-09</v>
+        <v>6.36055598036401e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.529760618086341e-09</v>
+        <v>7.529760618086349e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.871966377314148e-09</v>
+        <v>7.87196637731415e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.991173195424026e-09</v>
+        <v>7.991173195424024e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.029606438543826e-09</v>
+        <v>9.02960643854383e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>8.364720709440104e-09</v>
+        <v>8.364720709440101e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>5.989207420614327e-09</v>
+        <v>5.989207420614337e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.244067649156994e-09</v>
+        <v>5.244067649157007e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.166495117819786e-09</v>
+        <v>7.166495117819783e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.145353075086879e-09</v>
+        <v>7.145353075086878e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.536278994306736e-09</v>
+        <v>7.536278994306749e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>6.684366327164934e-09</v>
+        <v>6.684366327164932e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>6.40530256047736e-09</v>
+        <v>6.405302560477354e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>6.965420385092137e-09</v>
+        <v>6.965420385092131e-09</v>
       </c>
       <c r="V4" t="n">
         <v>5.752292044172415e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>9.502051008832368e-09</v>
+        <v>9.502051008832374e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.000577047925974e-08</v>
+        <v>1.000577047925973e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.207745326639896e-08</v>
+        <v>1.207745326639894e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.300846191083317e-09</v>
+        <v>6.300846191083319e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.53805844898336e-09</v>
+        <v>6.538058448983364e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.73985332712934e-08</v>
+        <v>1.739853327129342e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.844307078185354e-09</v>
+        <v>4.844307078185365e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>7.6927828896375e-09</v>
+        <v>7.692782889637521e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>7.6927828896375e-09</v>
+        <v>7.692782889637521e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.176053544749314e-09</v>
+        <v>6.176053544749324e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.288066318813084e-09</v>
+        <v>5.2880663188131e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>8.283432905262134e-09</v>
+        <v>8.283432905262149e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>7.6927828896375e-09</v>
+        <v>7.692782889637521e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>7.6927828896375e-09</v>
+        <v>7.692782889637521e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>7.692449867339696e-09</v>
+        <v>7.692449867339706e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6927828896375e-09</v>
+        <v>7.692782889637521e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>7.692782889637498e-09</v>
+        <v>7.692782889637521e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>7.692782889637318e-09</v>
+        <v>7.692782889637341e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.989207420614327e-09</v>
+        <v>5.484737596233036e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>6.091527615184401e-09</v>
+        <v>6.091527615184421e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.942788719416837e-09</v>
+        <v>5.942788719416853e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.284516567856205e-09</v>
+        <v>4.284516567856214e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>7.6927828896375e-09</v>
+        <v>7.692782889637521e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>7.6927828896375e-09</v>
+        <v>7.692782889637521e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>7.6927828896375e-09</v>
+        <v>7.692782889637521e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>6.302747571363207e-09</v>
+        <v>6.302747571363221e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>6.913615688591133e-09</v>
+        <v>6.913615688591154e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>7.693342697110226e-09</v>
+        <v>7.693342697110241e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.545585036201425e-09</v>
+        <v>4.545585036201437e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.052541552217664e-08</v>
+        <v>1.052541552217665e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.791395177550209e-09</v>
+        <v>4.791395177550219e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.6927828896375e-09</v>
+        <v>7.692782889637521e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.066825406070027e-08</v>
+        <v>1.06682540607003e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7886,85 +7886,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.710365990676908e-09</v>
+        <v>3.710365990676907e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>4.422812089276961e-09</v>
+        <v>4.422812089276959e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.501406458168389e-09</v>
+        <v>2.501406458168388e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.636578056004238e-09</v>
+        <v>4.636578056004242e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>4.636243849418993e-09</v>
+        <v>4.636243849419002e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.636576871716823e-09</v>
+        <v>4.636576871716813e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>5.989207420614327e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>4.943523521682946e-09</v>
+        <v>4.94352352168295e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>5.010278894170558e-09</v>
+        <v>5.010278894170562e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.636578056004238e-09</v>
+        <v>4.636578056004242e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>5.704473751562512e-09</v>
+        <v>5.704473751562516e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="Z6" t="n">
         <v>4.078154542602346e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.636576871716822e-09</v>
+        <v>4.636576871716812e-09</v>
       </c>
     </row>
     <row r="7">
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.413532319098706e-09</v>
+        <v>1.413532319098707e-09</v>
       </c>
       <c r="C7" t="n">
         <v>1.420035260346998e-09</v>
@@ -7983,7 +7983,7 @@
         <v>1.387337756941514e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.946799350082434e-09</v>
+        <v>1.946799350082432e-09</v>
       </c>
       <c r="F7" t="n">
         <v>1.405750517365448e-09</v>
@@ -7995,34 +7995,34 @@
         <v>1.422412595144541e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>1.392405657410114e-09</v>
+        <v>1.392405657410112e-09</v>
       </c>
       <c r="J7" t="n">
         <v>1.363796954852606e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>1.371706065879495e-09</v>
+        <v>1.371706065879494e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>1.338473725627694e-09</v>
+        <v>1.338473725627693e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3688332864695e-09</v>
+        <v>1.368833286469501e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.422387193271505e-09</v>
+        <v>1.422387193271504e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.433103041804358e-09</v>
+        <v>1.433103041804359e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.382302669524216e-09</v>
+        <v>1.382302669524217e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.390267350093255e-09</v>
+        <v>1.390267350093256e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>1.394294838588451e-09</v>
+        <v>1.39429483858845e-09</v>
       </c>
       <c r="S7" t="n">
         <v>1.394597569804624e-09</v>
@@ -8031,28 +8031,28 @@
         <v>1.41614147667953e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.392285648081346e-09</v>
+        <v>1.392285648081345e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.292567308536165e-09</v>
+        <v>1.292567308536164e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.338421931627778e-09</v>
+        <v>1.338421931627776e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.329374111772716e-09</v>
+        <v>1.329374111772715e-09</v>
       </c>
       <c r="Y7" t="n">
         <v>1.277519593778594e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.403770324487447e-09</v>
+        <v>1.403770324487448e-09</v>
       </c>
       <c r="AA7" t="n">
         <v>1.407884824045512e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.182874830490459e-09</v>
+        <v>1.182874830490458e-09</v>
       </c>
     </row>
     <row r="8">
@@ -8062,13 +8062,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.45212602836186e-09</v>
+        <v>1.452126028361859e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>1.454165379374167e-09</v>
+        <v>1.454165379374168e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>1.444884072719722e-09</v>
+        <v>1.444884072719721e-09</v>
       </c>
       <c r="E8" t="n">
         <v>1.968175338567626e-09</v>
@@ -8077,67 +8077,67 @@
         <v>1.450190286986465e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>1.422126841054707e-09</v>
+        <v>1.422126841054708e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>1.454935495865311e-09</v>
+        <v>1.454935495865309e-09</v>
       </c>
       <c r="I8" t="n">
         <v>1.446356475517542e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.435345827582362e-09</v>
+        <v>1.435345827582363e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>1.440411384714559e-09</v>
+        <v>1.44041138471456e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.430753064992851e-09</v>
+        <v>1.43075306499285e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>1.439703254783145e-09</v>
+        <v>1.439703254783146e-09</v>
       </c>
       <c r="N8" t="n">
         <v>1.454798452519723e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>1.457730415967307e-09</v>
+        <v>1.457730415967309e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>1.443129658592149e-09</v>
+        <v>1.443129658592148e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.445672842297913e-09</v>
+        <v>1.445672842297915e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.446927443523663e-09</v>
+        <v>1.446927443523661e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>1.446743787896585e-09</v>
+        <v>1.446743787896584e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.453080659118354e-09</v>
+        <v>1.453080659118352e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>1.446118565259557e-09</v>
+        <v>1.446118565259555e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.334259394741702e-09</v>
+        <v>1.334259394741701e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.430781452369419e-09</v>
+        <v>1.43078145236942e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.428379330241555e-09</v>
+        <v>1.428379330241553e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.413448278438572e-09</v>
+        <v>1.41344827843857e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.449341563782967e-09</v>
+        <v>1.449341563782966e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.450629492510088e-09</v>
+        <v>1.45062949251009e-09</v>
       </c>
       <c r="AB8" t="n">
         <v>1.386770367345393e-09</v>
